--- a/LunaRune64_0.7rc.xlsx
+++ b/LunaRune64_0.7rc.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8664"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8664" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3258" uniqueCount="1902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="1915">
   <si>
     <t>編號</t>
   </si>
@@ -2584,12 +2584,6 @@
     <t>結果・後果・完成</t>
   </si>
   <si>
-    <t>創生・變化・破序</t>
-  </si>
-  <si>
-    <t>順勢・承接・軌跡</t>
-  </si>
-  <si>
     <t>晶體／結晶；精華與純化，重點是純度提高。</t>
   </si>
   <si>
@@ -6045,22 +6039,66 @@
   </si>
   <si>
     <t>記憶・回溯・回憶</t>
+  </si>
+  <si>
+    <t>範圍・領域・疆域</t>
+  </si>
+  <si>
+    <t>映照・映射・洞察</t>
+  </si>
+  <si>
+    <t>核心・本質・中央</t>
+  </si>
+  <si>
+    <t>方向・前進・趨勢</t>
+  </si>
+  <si>
+    <t>切斷・中止・斷絕</t>
+  </si>
+  <si>
+    <t>封存・封閉・暫斷</t>
+  </si>
+  <si>
+    <t>分離・分割・拆分</t>
+  </si>
+  <si>
+    <t>錯誤・誤判・偏離</t>
+  </si>
+  <si>
+    <t>疾病・失衡・病痛</t>
+  </si>
+  <si>
+    <t>死亡・終止・終結</t>
+  </si>
+  <si>
+    <t>塵埃・微粒・殘餘</t>
+  </si>
+  <si>
+    <t>陰影・低調・內斂</t>
+  </si>
+  <si>
+    <t>日蝕・遮蔽・消隱</t>
+  </si>
+  <si>
+    <t>災禍・危機・警告</t>
+  </si>
+  <si>
+    <t>幻覺・失真・錯認</t>
+  </si>
+  <si>
+    <t>月蝕・暗面・陰狠</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>範圍・領域・疆域</t>
+    <t>虛空・空洞・虛無</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>映照・映射・洞察</t>
+    <t>混沌・變化・破序</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>核心・本質・中央</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>方向・前進・趨勢</t>
+    <t>順勢・承接・規則</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -6107,6 +6145,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -6125,6 +6164,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -7737,19 +7777,15 @@
     <cellStyle name="好" xfId="4"/>
     <cellStyle name="備註" xfId="6"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="61">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="微軟正黑體 Light"/>
         <scheme val="none"/>
@@ -7757,13 +7793,17 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <u val="none"/>
+        <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="微軟正黑體 Light"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -7774,150 +7814,6 @@
           <color auto="1"/>
         </top>
         <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -7932,7 +7828,7 @@
         <name val="微軟正黑體 Light"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -7942,12 +7838,93 @@
         <top style="thin">
           <color auto="1"/>
         </top>
-        <bottom style="medium">
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <left style="medium">
           <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -7998,7 +7975,34 @@
         <name val="微軟正黑體 Light"/>
         <scheme val="none"/>
       </font>
-      <border outline="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -8312,6 +8316,60 @@
         <u val="none"/>
         <sz val="12"/>
         <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
         <name val="新細明體"/>
         <scheme val="none"/>
       </font>
@@ -8411,60 +8469,6 @@
         <name val="微軟正黑體 Light"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
       <border>
         <left style="thin">
           <color auto="1"/>
@@ -8497,6 +8501,119 @@
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="微軟正黑體 Light"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -8898,57 +9015,6 @@
         <name val="微軟正黑體 Light"/>
         <scheme val="none"/>
       </font>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="微軟正黑體 Light"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill>
@@ -9129,48 +9195,48 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表格1" displayName="表格1" ref="A1:J67" totalsRowShown="0" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表格1" displayName="表格1" ref="A1:J67" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:J67"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="編號" dataDxfId="18"/>
-    <tableColumn id="2" name="符文名稱" dataDxfId="17"/>
-    <tableColumn id="3" name="英文" dataDxfId="16"/>
-    <tableColumn id="4" name="圖騰" dataDxfId="15"/>
-    <tableColumn id="5" name="所屬分組" dataDxfId="14"/>
-    <tableColumn id="6" name="月相" dataDxfId="13"/>
-    <tableColumn id="7" name="卡片屬性" dataDxfId="12"/>
-    <tableColumn id="8" name="靈魂咒語" dataDxfId="8"/>
-    <tableColumn id="9" name="關鍵詞" dataDxfId="11"/>
-    <tableColumn id="10" name="人格原型" dataDxfId="10"/>
+    <tableColumn id="1" name="編號" dataDxfId="17"/>
+    <tableColumn id="2" name="符文名稱" dataDxfId="16"/>
+    <tableColumn id="3" name="英文" dataDxfId="15"/>
+    <tableColumn id="4" name="圖騰" dataDxfId="14"/>
+    <tableColumn id="5" name="所屬分組" dataDxfId="13"/>
+    <tableColumn id="6" name="月相" dataDxfId="12"/>
+    <tableColumn id="7" name="卡片屬性" dataDxfId="11"/>
+    <tableColumn id="8" name="靈魂咒語" dataDxfId="10"/>
+    <tableColumn id="9" name="關鍵詞" dataDxfId="9"/>
+    <tableColumn id="10" name="人格原型" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表格2" displayName="表格2" ref="A1:F67" totalsRowShown="0" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表格2" displayName="表格2" ref="A1:F67" totalsRowShown="0" dataDxfId="60">
   <autoFilter ref="A1:F67"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="編號" dataDxfId="58"/>
-    <tableColumn id="2" name="符文名稱" dataDxfId="57"/>
-    <tableColumn id="3" name="圖騰" dataDxfId="56"/>
-    <tableColumn id="5" name="所屬分組" dataDxfId="55"/>
-    <tableColumn id="6" name="月相" dataDxfId="54"/>
-    <tableColumn id="7" name="特別說明" dataDxfId="53"/>
+    <tableColumn id="1" name="編號" dataDxfId="59"/>
+    <tableColumn id="2" name="符文名稱" dataDxfId="58"/>
+    <tableColumn id="3" name="圖騰" dataDxfId="57"/>
+    <tableColumn id="5" name="所屬分組" dataDxfId="56"/>
+    <tableColumn id="6" name="月相" dataDxfId="55"/>
+    <tableColumn id="7" name="特別說明" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="表格3" displayName="表格3" ref="A1:E67" totalsRowShown="0" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="表格3" displayName="表格3" ref="A1:E67" totalsRowShown="0" dataDxfId="0">
   <autoFilter ref="A1:E67"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="名稱" dataDxfId="51"/>
-    <tableColumn id="2" name="圖騰" dataDxfId="50"/>
-    <tableColumn id="4" name="反向關鍵字" dataDxfId="5"/>
-    <tableColumn id="5" name="陰影面" dataDxfId="6"/>
-    <tableColumn id="6" name="反向含義" dataDxfId="7"/>
+    <tableColumn id="1" name="名稱" dataDxfId="5"/>
+    <tableColumn id="2" name="圖騰" dataDxfId="4"/>
+    <tableColumn id="4" name="反向關鍵字" dataDxfId="3"/>
+    <tableColumn id="5" name="陰影面" dataDxfId="2"/>
+    <tableColumn id="6" name="反向含義" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9180,33 +9246,33 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="表格4" displayName="表格4" ref="A1:G67" totalsRowShown="0">
   <autoFilter ref="A1:G67"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="編號" dataDxfId="49"/>
-    <tableColumn id="2" name="名稱" dataDxfId="48"/>
-    <tableColumn id="3" name="圖騰" dataDxfId="47"/>
-    <tableColumn id="4" name="所屬分組" dataDxfId="46"/>
-    <tableColumn id="5" name="月相" dataDxfId="45"/>
-    <tableColumn id="6" name="符文變化歷史" dataDxfId="44"/>
-    <tableColumn id="7" name="神話故事" dataDxfId="43"/>
+    <tableColumn id="1" name="編號" dataDxfId="53"/>
+    <tableColumn id="2" name="名稱" dataDxfId="52"/>
+    <tableColumn id="3" name="圖騰" dataDxfId="51"/>
+    <tableColumn id="4" name="所屬分組" dataDxfId="50"/>
+    <tableColumn id="5" name="月相" dataDxfId="49"/>
+    <tableColumn id="6" name="符文變化歷史" dataDxfId="48"/>
+    <tableColumn id="7" name="神話故事" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="表格5" displayName="表格5" ref="A1:I67" totalsRowShown="0" headerRowBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="表格5" displayName="表格5" ref="A1:I67" totalsRowShown="0" headerRowBorderDxfId="46">
   <autoFilter ref="A1:I67"/>
   <tableColumns count="9">
-    <tableColumn id="1" name="名稱" dataDxfId="41"/>
-    <tableColumn id="2" name="圖騰" dataDxfId="40"/>
-    <tableColumn id="3" name="所屬分組" dataDxfId="39"/>
-    <tableColumn id="4" name="月相" dataDxfId="38"/>
-    <tableColumn id="5" name="具象插圖背景" dataDxfId="37"/>
-    <tableColumn id="6" name="圖編號" dataDxfId="36"/>
-    <tableColumn id="7" name="圖檔名稱" dataDxfId="35">
+    <tableColumn id="1" name="名稱" dataDxfId="45"/>
+    <tableColumn id="2" name="圖騰" dataDxfId="44"/>
+    <tableColumn id="3" name="所屬分組" dataDxfId="43"/>
+    <tableColumn id="4" name="月相" dataDxfId="42"/>
+    <tableColumn id="5" name="具象插圖背景" dataDxfId="41"/>
+    <tableColumn id="6" name="圖編號" dataDxfId="40"/>
+    <tableColumn id="7" name="圖檔名稱" dataDxfId="39">
       <calculatedColumnFormula>CONCATENATE(F2,A2,".png")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="符文底圖代碼" dataDxfId="34"/>
-    <tableColumn id="9" name="符文卡圖代碼" dataDxfId="33"/>
+    <tableColumn id="8" name="符文底圖代碼" dataDxfId="38"/>
+    <tableColumn id="9" name="符文卡圖代碼" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9216,13 +9282,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="表格6" displayName="表格6" ref="A1:G67" totalsRowShown="0">
   <autoFilter ref="A1:G67"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="編號" dataDxfId="32"/>
-    <tableColumn id="2" name="名稱" dataDxfId="31"/>
-    <tableColumn id="6" name="靈魂課題" dataDxfId="4"/>
-    <tableColumn id="7" name="實踐挑戰" dataDxfId="3"/>
-    <tableColumn id="8" name="配套儀式建議" dataDxfId="2"/>
-    <tableColumn id="9" name="能量調和建議" dataDxfId="1"/>
-    <tableColumn id="10" name="欄1" dataDxfId="0"/>
+    <tableColumn id="1" name="編號" dataDxfId="36"/>
+    <tableColumn id="2" name="名稱" dataDxfId="35"/>
+    <tableColumn id="6" name="靈魂課題" dataDxfId="34"/>
+    <tableColumn id="7" name="實踐挑戰" dataDxfId="33"/>
+    <tableColumn id="8" name="配套儀式建議" dataDxfId="32"/>
+    <tableColumn id="9" name="能量調和建議" dataDxfId="31"/>
+    <tableColumn id="10" name="欄1" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9232,12 +9298,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="表格7" displayName="表格7" ref="A1:F67" totalsRowShown="0" headerRowCellStyle="40% - 輔色1">
   <autoFilter ref="A1:F67"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="編號" dataDxfId="30"/>
-    <tableColumn id="2" name="名稱" dataDxfId="29"/>
-    <tableColumn id="3" name="正向表示" dataDxfId="26" dataCellStyle="20% - 輔色1"/>
-    <tableColumn id="4" name="半正向表示" dataDxfId="25" dataCellStyle="40% - 輔色1"/>
-    <tableColumn id="5" name="半逆向表示" dataDxfId="24" dataCellStyle="20% - 輔色2"/>
-    <tableColumn id="6" name="逆向表示" dataDxfId="23" dataCellStyle="40% - 輔色2"/>
+    <tableColumn id="1" name="編號" dataDxfId="29"/>
+    <tableColumn id="2" name="名稱" dataDxfId="28"/>
+    <tableColumn id="3" name="正向表示" dataDxfId="27" dataCellStyle="20% - 輔色1"/>
+    <tableColumn id="4" name="半正向表示" dataDxfId="26" dataCellStyle="40% - 輔色1"/>
+    <tableColumn id="5" name="半逆向表示" dataDxfId="25" dataCellStyle="20% - 輔色2"/>
+    <tableColumn id="6" name="逆向表示" dataDxfId="24" dataCellStyle="40% - 輔色2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9247,12 +9313,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="表格8" displayName="表格8" ref="A1:F67" totalsRowShown="0">
   <autoFilter ref="A1:F67"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="編號" dataDxfId="28"/>
-    <tableColumn id="2" name="名稱" dataDxfId="27"/>
-    <tableColumn id="3" name="正向表示" dataDxfId="22"/>
-    <tableColumn id="4" name="半正向表示" dataDxfId="21"/>
-    <tableColumn id="5" name="半逆向表示" dataDxfId="20"/>
-    <tableColumn id="6" name="逆向表示" dataDxfId="19"/>
+    <tableColumn id="1" name="編號" dataDxfId="23"/>
+    <tableColumn id="2" name="名稱" dataDxfId="22"/>
+    <tableColumn id="3" name="正向表示" dataDxfId="21"/>
+    <tableColumn id="4" name="半正向表示" dataDxfId="20"/>
+    <tableColumn id="5" name="半逆向表示" dataDxfId="19"/>
+    <tableColumn id="6" name="逆向表示" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9475,7 +9541,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N67"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="19.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" style="33" customWidth="1"/>
     <col min="2" max="2" width="13.375" style="33" customWidth="1"/>
@@ -9485,7 +9551,7 @@
     <col min="6" max="6" width="8.5" style="33" customWidth="1"/>
     <col min="7" max="7" width="13.75" style="33" customWidth="1"/>
     <col min="8" max="8" width="34.125" style="33" customWidth="1"/>
-    <col min="9" max="9" width="27" style="33" customWidth="1"/>
+    <col min="9" max="9" width="27" style="97" customWidth="1"/>
     <col min="10" max="10" width="13.75" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="14" width="28" customWidth="1"/>
@@ -9549,7 +9615,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="98" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="I2" s="98" t="s">
         <v>788</v>
@@ -9584,7 +9650,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="99" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="I3" s="99" t="s">
         <v>789</v>
@@ -9619,7 +9685,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="99" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="I4" s="99" t="s">
         <v>790</v>
@@ -9654,10 +9720,10 @@
         <v>21</v>
       </c>
       <c r="H5" s="99" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="I5" s="99" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="J5" s="112" t="s">
         <v>30</v>
@@ -9689,7 +9755,7 @@
         <v>21</v>
       </c>
       <c r="H6" s="99" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="I6" s="99" t="s">
         <v>791</v>
@@ -9724,10 +9790,10 @@
         <v>21</v>
       </c>
       <c r="H7" s="99" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="I7" s="99" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="J7" s="112" t="s">
         <v>40</v>
@@ -9759,10 +9825,10 @@
         <v>15</v>
       </c>
       <c r="H8" s="99" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="I8" s="99" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="J8" s="112" t="s">
         <v>44</v>
@@ -9794,10 +9860,10 @@
         <v>15</v>
       </c>
       <c r="H9" s="100" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="I9" s="100" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="J9" s="114" t="s">
         <v>48</v>
@@ -9829,10 +9895,10 @@
         <v>21</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="I10" s="98" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="J10" s="110" t="s">
         <v>53</v>
@@ -9864,9 +9930,11 @@
         <v>57</v>
       </c>
       <c r="H11" s="99" t="s">
-        <v>1377</v>
-      </c>
-      <c r="I11" s="99"/>
+        <v>1375</v>
+      </c>
+      <c r="I11" s="99" t="s">
+        <v>1900</v>
+      </c>
       <c r="J11" s="112" t="s">
         <v>58</v>
       </c>
@@ -9897,9 +9965,11 @@
         <v>57</v>
       </c>
       <c r="H12" s="99" t="s">
-        <v>1378</v>
-      </c>
-      <c r="I12" s="99"/>
+        <v>1376</v>
+      </c>
+      <c r="I12" s="99" t="s">
+        <v>1901</v>
+      </c>
       <c r="J12" s="112" t="s">
         <v>62</v>
       </c>
@@ -9930,7 +10000,7 @@
         <v>21</v>
       </c>
       <c r="H13" s="99" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="I13" s="99" t="s">
         <v>792</v>
@@ -9965,7 +10035,7 @@
         <v>15</v>
       </c>
       <c r="H14" s="99" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="I14" s="99" t="s">
         <v>793</v>
@@ -10000,9 +10070,11 @@
         <v>57</v>
       </c>
       <c r="H15" s="99" t="s">
-        <v>1380</v>
-      </c>
-      <c r="I15" s="99"/>
+        <v>1378</v>
+      </c>
+      <c r="I15" s="99" t="s">
+        <v>1902</v>
+      </c>
       <c r="J15" s="112" t="s">
         <v>74</v>
       </c>
@@ -10068,9 +10140,11 @@
         <v>57</v>
       </c>
       <c r="H17" s="101" t="s">
-        <v>1381</v>
-      </c>
-      <c r="I17" s="100"/>
+        <v>1379</v>
+      </c>
+      <c r="I17" s="100" t="s">
+        <v>1903</v>
+      </c>
       <c r="J17" s="114" t="s">
         <v>83</v>
       </c>
@@ -10101,7 +10175,7 @@
         <v>15</v>
       </c>
       <c r="H18" s="98" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="I18" s="98" t="s">
         <v>795</v>
@@ -10136,7 +10210,7 @@
         <v>15</v>
       </c>
       <c r="H19" s="99" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="I19" s="99" t="s">
         <v>796</v>
@@ -10171,9 +10245,11 @@
         <v>57</v>
       </c>
       <c r="H20" s="99" t="s">
-        <v>1384</v>
-      </c>
-      <c r="I20" s="99"/>
+        <v>1382</v>
+      </c>
+      <c r="I20" s="99" t="s">
+        <v>1904</v>
+      </c>
       <c r="J20" s="112" t="s">
         <v>96</v>
       </c>
@@ -10204,9 +10280,11 @@
         <v>57</v>
       </c>
       <c r="H21" s="99" t="s">
-        <v>1385</v>
-      </c>
-      <c r="I21" s="99"/>
+        <v>1383</v>
+      </c>
+      <c r="I21" s="99" t="s">
+        <v>1905</v>
+      </c>
       <c r="J21" s="112" t="s">
         <v>100</v>
       </c>
@@ -10237,7 +10315,7 @@
         <v>15</v>
       </c>
       <c r="H22" s="99" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="I22" s="99" t="s">
         <v>797</v>
@@ -10272,7 +10350,7 @@
         <v>15</v>
       </c>
       <c r="H23" s="99" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="I23" s="99" t="s">
         <v>798</v>
@@ -10307,7 +10385,7 @@
         <v>21</v>
       </c>
       <c r="H24" s="99" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="I24" s="99" t="s">
         <v>799</v>
@@ -10342,7 +10420,7 @@
         <v>15</v>
       </c>
       <c r="H25" s="100" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="I25" s="100" t="s">
         <v>800</v>
@@ -10377,7 +10455,7 @@
         <v>15</v>
       </c>
       <c r="H26" s="98" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="I26" s="98" t="s">
         <v>801</v>
@@ -10412,7 +10490,7 @@
         <v>15</v>
       </c>
       <c r="H27" s="99" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="I27" s="99" t="s">
         <v>802</v>
@@ -10447,7 +10525,7 @@
         <v>21</v>
       </c>
       <c r="H28" s="99" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="I28" s="99" t="s">
         <v>803</v>
@@ -10482,7 +10560,7 @@
         <v>21</v>
       </c>
       <c r="H29" s="99" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="I29" s="99" t="s">
         <v>804</v>
@@ -10517,7 +10595,7 @@
         <v>15</v>
       </c>
       <c r="H30" s="99" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="I30" s="99" t="s">
         <v>805</v>
@@ -10552,7 +10630,7 @@
         <v>21</v>
       </c>
       <c r="H31" s="99" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="I31" s="99" t="s">
         <v>806</v>
@@ -10587,7 +10665,7 @@
         <v>21</v>
       </c>
       <c r="H32" s="99" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="I32" s="99" t="s">
         <v>807</v>
@@ -10622,7 +10700,7 @@
         <v>21</v>
       </c>
       <c r="H33" s="100" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="I33" s="100" t="s">
         <v>808</v>
@@ -10657,7 +10735,7 @@
         <v>21</v>
       </c>
       <c r="H34" s="38" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="I34" s="98" t="s">
         <v>809</v>
@@ -10692,7 +10770,7 @@
         <v>15</v>
       </c>
       <c r="H35" s="99" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="I35" s="99" t="s">
         <v>810</v>
@@ -10727,7 +10805,7 @@
         <v>15</v>
       </c>
       <c r="H36" s="99" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="I36" s="99" t="s">
         <v>811</v>
@@ -10762,7 +10840,7 @@
         <v>15</v>
       </c>
       <c r="H37" s="99" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="I37" s="99" t="s">
         <v>812</v>
@@ -10797,7 +10875,7 @@
         <v>15</v>
       </c>
       <c r="H38" s="99" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="I38" s="99" t="s">
         <v>813</v>
@@ -10832,7 +10910,7 @@
         <v>21</v>
       </c>
       <c r="H39" s="99" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="I39" s="99" t="s">
         <v>814</v>
@@ -10867,7 +10945,7 @@
         <v>21</v>
       </c>
       <c r="H40" s="99" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="I40" s="99" t="s">
         <v>815</v>
@@ -10902,9 +10980,11 @@
         <v>57</v>
       </c>
       <c r="H41" s="101" t="s">
-        <v>1405</v>
-      </c>
-      <c r="I41" s="100"/>
+        <v>1403</v>
+      </c>
+      <c r="I41" s="100" t="s">
+        <v>1906</v>
+      </c>
       <c r="J41" s="114" t="s">
         <v>181</v>
       </c>
@@ -10935,7 +11015,7 @@
         <v>15</v>
       </c>
       <c r="H42" s="98" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="I42" s="98" t="s">
         <v>816</v>
@@ -10970,9 +11050,11 @@
         <v>57</v>
       </c>
       <c r="H43" s="99" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I43" s="99"/>
+        <v>1405</v>
+      </c>
+      <c r="I43" s="99" t="s">
+        <v>1907</v>
+      </c>
       <c r="J43" s="112" t="s">
         <v>190</v>
       </c>
@@ -11003,7 +11085,7 @@
         <v>21</v>
       </c>
       <c r="H44" s="99" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="I44" s="99" t="s">
         <v>817</v>
@@ -11038,7 +11120,7 @@
         <v>21</v>
       </c>
       <c r="H45" s="99" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="I45" s="99" t="s">
         <v>818</v>
@@ -11073,7 +11155,7 @@
         <v>21</v>
       </c>
       <c r="H46" s="99" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="I46" s="99" t="s">
         <v>819</v>
@@ -11108,7 +11190,7 @@
         <v>21</v>
       </c>
       <c r="H47" s="99" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="I47" s="99" t="s">
         <v>820</v>
@@ -11143,7 +11225,7 @@
         <v>21</v>
       </c>
       <c r="H48" s="99" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="I48" s="99" t="s">
         <v>821</v>
@@ -11178,7 +11260,7 @@
         <v>21</v>
       </c>
       <c r="H49" s="100" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="I49" s="100" t="s">
         <v>822</v>
@@ -11213,9 +11295,11 @@
         <v>57</v>
       </c>
       <c r="H50" s="38" t="s">
-        <v>1414</v>
-      </c>
-      <c r="I50" s="98"/>
+        <v>1412</v>
+      </c>
+      <c r="I50" s="98" t="s">
+        <v>1908</v>
+      </c>
       <c r="J50" s="110" t="s">
         <v>219</v>
       </c>
@@ -11246,9 +11330,11 @@
         <v>57</v>
       </c>
       <c r="H51" s="99" t="s">
-        <v>1415</v>
-      </c>
-      <c r="I51" s="99"/>
+        <v>1413</v>
+      </c>
+      <c r="I51" s="99" t="s">
+        <v>1911</v>
+      </c>
       <c r="J51" s="112" t="s">
         <v>223</v>
       </c>
@@ -11279,7 +11365,7 @@
         <v>21</v>
       </c>
       <c r="H52" s="99" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="I52" s="99" t="s">
         <v>823</v>
@@ -11314,7 +11400,7 @@
         <v>21</v>
       </c>
       <c r="H53" s="99" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="I53" s="99" t="s">
         <v>824</v>
@@ -11349,7 +11435,7 @@
         <v>15</v>
       </c>
       <c r="H54" s="99" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="I54" s="99" t="s">
         <v>825</v>
@@ -11384,7 +11470,7 @@
         <v>21</v>
       </c>
       <c r="H55" s="99" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="I55" s="99" t="s">
         <v>826</v>
@@ -11419,7 +11505,7 @@
         <v>21</v>
       </c>
       <c r="H56" s="99" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="I56" s="99" t="s">
         <v>827</v>
@@ -11454,7 +11540,7 @@
         <v>21</v>
       </c>
       <c r="H57" s="101" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="I57" s="100" t="s">
         <v>828</v>
@@ -11489,7 +11575,7 @@
         <v>15</v>
       </c>
       <c r="H58" s="98" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="I58" s="98" t="s">
         <v>829</v>
@@ -11524,9 +11610,11 @@
         <v>57</v>
       </c>
       <c r="H59" s="99" t="s">
-        <v>1423</v>
-      </c>
-      <c r="I59" s="99"/>
+        <v>1421</v>
+      </c>
+      <c r="I59" s="99" t="s">
+        <v>1909</v>
+      </c>
       <c r="J59" s="112" t="s">
         <v>256</v>
       </c>
@@ -11557,7 +11645,7 @@
         <v>260</v>
       </c>
       <c r="H60" s="99" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="I60" s="99" t="s">
         <v>830</v>
@@ -11592,7 +11680,7 @@
         <v>15</v>
       </c>
       <c r="H61" s="99" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="I61" s="99" t="s">
         <v>831</v>
@@ -11627,9 +11715,11 @@
         <v>57</v>
       </c>
       <c r="H62" s="99" t="s">
-        <v>1426</v>
-      </c>
-      <c r="I62" s="99"/>
+        <v>1424</v>
+      </c>
+      <c r="I62" s="99" t="s">
+        <v>1910</v>
+      </c>
       <c r="J62" s="112" t="s">
         <v>269</v>
       </c>
@@ -11660,7 +11750,7 @@
         <v>21</v>
       </c>
       <c r="H63" s="99" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="I63" s="99" t="s">
         <v>832</v>
@@ -11695,9 +11785,11 @@
         <v>57</v>
       </c>
       <c r="H64" s="99" t="s">
-        <v>1428</v>
-      </c>
-      <c r="I64" s="99"/>
+        <v>1426</v>
+      </c>
+      <c r="I64" s="99" t="s">
+        <v>1912</v>
+      </c>
       <c r="J64" s="112" t="s">
         <v>277</v>
       </c>
@@ -11728,7 +11820,7 @@
         <v>21</v>
       </c>
       <c r="H65" s="100" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="I65" s="100" t="s">
         <v>833</v>
@@ -11763,10 +11855,10 @@
         <v>260</v>
       </c>
       <c r="H66" s="98" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="I66" s="98" t="s">
-        <v>834</v>
+        <v>1913</v>
       </c>
       <c r="J66" s="110" t="s">
         <v>286</v>
@@ -11798,10 +11890,10 @@
         <v>260</v>
       </c>
       <c r="H67" s="100" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="I67" s="100" t="s">
-        <v>835</v>
+        <v>1914</v>
       </c>
       <c r="J67" s="114" t="s">
         <v>289</v>
@@ -12848,7 +12940,7 @@
         <v>34</v>
       </c>
       <c r="F36" s="129" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="66" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13408,7 +13500,7 @@
         <v>39</v>
       </c>
       <c r="F64" s="129" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="66" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13509,7 +13601,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="52" t="s">
         <v>10</v>
       </c>
@@ -13517,16 +13609,16 @@
         <v>12</v>
       </c>
       <c r="C2" s="98" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="D2" s="98" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>1433</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
         <v>17</v>
       </c>
@@ -13534,16 +13626,16 @@
         <v>19</v>
       </c>
       <c r="C3" s="99" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D3" s="99" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>1434</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
         <v>23</v>
       </c>
@@ -13551,16 +13643,16 @@
         <v>25</v>
       </c>
       <c r="C4" s="99" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="D4" s="99" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="E4" s="112" t="s">
-        <v>1435</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53" t="s">
         <v>27</v>
       </c>
@@ -13568,16 +13660,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="99" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="D5" s="99" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="E5" s="112" t="s">
-        <v>1436</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
         <v>31</v>
       </c>
@@ -13585,16 +13677,16 @@
         <v>33</v>
       </c>
       <c r="C6" s="99" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="D6" s="99" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="E6" s="112" t="s">
-        <v>1437</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="53" t="s">
         <v>36</v>
       </c>
@@ -13602,16 +13694,16 @@
         <v>38</v>
       </c>
       <c r="C7" s="99" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="D7" s="99" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="E7" s="112" t="s">
-        <v>1438</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="53" t="s">
         <v>41</v>
       </c>
@@ -13619,16 +13711,16 @@
         <v>43</v>
       </c>
       <c r="C8" s="99" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="D8" s="99" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="E8" s="112" t="s">
-        <v>1439</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="55" t="s">
         <v>45</v>
       </c>
@@ -13636,16 +13728,16 @@
         <v>47</v>
       </c>
       <c r="C9" s="101" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="D9" s="101" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="E9" s="127" t="s">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="52" t="s">
         <v>49</v>
       </c>
@@ -13653,16 +13745,16 @@
         <v>51</v>
       </c>
       <c r="C10" s="98" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="D10" s="98" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="E10" s="110" t="s">
-        <v>1441</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="53" t="s">
         <v>54</v>
       </c>
@@ -13670,16 +13762,16 @@
         <v>56</v>
       </c>
       <c r="C11" s="99" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="D11" s="99" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="E11" s="112" t="s">
-        <v>1442</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="53" t="s">
         <v>59</v>
       </c>
@@ -13687,16 +13779,16 @@
         <v>61</v>
       </c>
       <c r="C12" s="99" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="D12" s="99" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="E12" s="112" t="s">
-        <v>1443</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="53" t="s">
         <v>63</v>
       </c>
@@ -13704,16 +13796,16 @@
         <v>65</v>
       </c>
       <c r="C13" s="99" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="D13" s="99" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="E13" s="112" t="s">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="53" t="s">
         <v>67</v>
       </c>
@@ -13721,16 +13813,16 @@
         <v>69</v>
       </c>
       <c r="C14" s="99" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="D14" s="99" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="E14" s="112" t="s">
-        <v>1445</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="53" t="s">
         <v>71</v>
       </c>
@@ -13738,16 +13830,16 @@
         <v>73</v>
       </c>
       <c r="C15" s="99" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="D15" s="99" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="E15" s="112" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="53" t="s">
         <v>75</v>
       </c>
@@ -13755,16 +13847,16 @@
         <v>77</v>
       </c>
       <c r="C16" s="99" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="D16" s="99" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="E16" s="112" t="s">
-        <v>1447</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="55" t="s">
         <v>80</v>
       </c>
@@ -13772,16 +13864,16 @@
         <v>82</v>
       </c>
       <c r="C17" s="101" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="D17" s="101" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="E17" s="127" t="s">
-        <v>1448</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>84</v>
       </c>
@@ -13789,16 +13881,16 @@
         <v>86</v>
       </c>
       <c r="C18" s="98" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="D18" s="98" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="E18" s="110" t="s">
-        <v>1449</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
         <v>89</v>
       </c>
@@ -13806,16 +13898,16 @@
         <v>91</v>
       </c>
       <c r="C19" s="99" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="D19" s="99" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="E19" s="112" t="s">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="20" t="s">
         <v>93</v>
       </c>
@@ -13823,16 +13915,16 @@
         <v>95</v>
       </c>
       <c r="C20" s="99" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="D20" s="99" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="E20" s="112" t="s">
-        <v>1451</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
         <v>97</v>
       </c>
@@ -13840,16 +13932,16 @@
         <v>99</v>
       </c>
       <c r="C21" s="99" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="D21" s="99" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="E21" s="112" t="s">
-        <v>1452</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
         <v>101</v>
       </c>
@@ -13857,16 +13949,16 @@
         <v>103</v>
       </c>
       <c r="C22" s="99" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="D22" s="99" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="E22" s="112" t="s">
-        <v>1453</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="20" t="s">
         <v>105</v>
       </c>
@@ -13874,16 +13966,16 @@
         <v>107</v>
       </c>
       <c r="C23" s="99" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="D23" s="99" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="E23" s="112" t="s">
-        <v>1454</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
         <v>109</v>
       </c>
@@ -13891,16 +13983,16 @@
         <v>111</v>
       </c>
       <c r="C24" s="99" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="D24" s="112" t="s">
-        <v>1521</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>1455</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1519</v>
+      </c>
+      <c r="E24" s="115" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
         <v>113</v>
       </c>
@@ -13908,16 +14000,16 @@
         <v>115</v>
       </c>
       <c r="C25" s="100" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="D25" s="100" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="E25" s="114" t="s">
-        <v>1456</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="38" t="s">
         <v>117</v>
       </c>
@@ -13925,16 +14017,16 @@
         <v>119</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>1457</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="35" t="s">
         <v>121</v>
       </c>
@@ -13942,16 +14034,16 @@
         <v>123</v>
       </c>
       <c r="C27" s="99" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="D27" s="99" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="E27" s="112" t="s">
-        <v>1458</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="35" t="s">
         <v>125</v>
       </c>
@@ -13959,16 +14051,16 @@
         <v>127</v>
       </c>
       <c r="C28" s="99" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D28" s="99" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="E28" s="112" t="s">
-        <v>1459</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="35" t="s">
         <v>129</v>
       </c>
@@ -13976,16 +14068,16 @@
         <v>131</v>
       </c>
       <c r="C29" s="99" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="D29" s="99" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="E29" s="112" t="s">
-        <v>1460</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="35" t="s">
         <v>133</v>
       </c>
@@ -13993,16 +14085,16 @@
         <v>135</v>
       </c>
       <c r="C30" s="99" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="D30" s="99" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="E30" s="112" t="s">
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="35" t="s">
         <v>137</v>
       </c>
@@ -14010,16 +14102,16 @@
         <v>139</v>
       </c>
       <c r="C31" s="99" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="D31" s="99" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="E31" s="112" t="s">
-        <v>1462</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="35" t="s">
         <v>141</v>
       </c>
@@ -14027,16 +14119,16 @@
         <v>143</v>
       </c>
       <c r="C32" s="99" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="D32" s="99" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="E32" s="112" t="s">
-        <v>1463</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="36" t="s">
         <v>145</v>
       </c>
@@ -14044,16 +14136,16 @@
         <v>147</v>
       </c>
       <c r="C33" s="101" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="D33" s="101" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="E33" s="127" t="s">
-        <v>1464</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
         <v>149</v>
       </c>
@@ -14061,16 +14153,16 @@
         <v>151</v>
       </c>
       <c r="C34" s="98" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="D34" s="98" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="E34" s="110" t="s">
-        <v>1465</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20" t="s">
         <v>154</v>
       </c>
@@ -14078,16 +14170,16 @@
         <v>156</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="D35" s="99" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="E35" s="112" t="s">
-        <v>1466</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20" t="s">
         <v>158</v>
       </c>
@@ -14095,16 +14187,16 @@
         <v>160</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="D36" s="99" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="E36" s="112" t="s">
-        <v>1467</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20" t="s">
         <v>162</v>
       </c>
@@ -14112,16 +14204,16 @@
         <v>164</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="D37" s="99" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="E37" s="112" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="20" t="s">
         <v>166</v>
       </c>
@@ -14129,16 +14221,16 @@
         <v>168</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="D38" s="99" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="E38" s="112" t="s">
-        <v>1469</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="20" t="s">
         <v>170</v>
       </c>
@@ -14146,16 +14238,16 @@
         <v>172</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="D39" s="99" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="E39" s="112" t="s">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="20" t="s">
         <v>174</v>
       </c>
@@ -14163,16 +14255,16 @@
         <v>176</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="D40" s="99" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="E40" s="112" t="s">
-        <v>1471</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="21" t="s">
         <v>178</v>
       </c>
@@ -14180,16 +14272,16 @@
         <v>180</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="D41" s="100" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="E41" s="114" t="s">
-        <v>1472</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="38" t="s">
         <v>182</v>
       </c>
@@ -14197,16 +14289,16 @@
         <v>184</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="E42" s="42" t="s">
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="35" t="s">
         <v>187</v>
       </c>
@@ -14214,16 +14306,16 @@
         <v>189</v>
       </c>
       <c r="C43" s="99" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="D43" s="99" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="E43" s="112" t="s">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="35" t="s">
         <v>191</v>
       </c>
@@ -14231,16 +14323,16 @@
         <v>193</v>
       </c>
       <c r="C44" s="99" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="D44" s="99" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="E44" s="112" t="s">
-        <v>1475</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="35" t="s">
         <v>195</v>
       </c>
@@ -14248,16 +14340,16 @@
         <v>197</v>
       </c>
       <c r="C45" s="99" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="D45" s="99" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="E45" s="112" t="s">
-        <v>1476</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="35" t="s">
         <v>199</v>
       </c>
@@ -14265,16 +14357,16 @@
         <v>201</v>
       </c>
       <c r="C46" s="99" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="D46" s="99" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="E46" s="112" t="s">
-        <v>1477</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
         <v>203</v>
       </c>
@@ -14282,16 +14374,16 @@
         <v>205</v>
       </c>
       <c r="C47" s="99" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="D47" s="99" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="E47" s="112" t="s">
-        <v>1478</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="35" t="s">
         <v>207</v>
       </c>
@@ -14299,16 +14391,16 @@
         <v>209</v>
       </c>
       <c r="C48" s="99" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="D48" s="112" t="s">
-        <v>1545</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>1479</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1543</v>
+      </c>
+      <c r="E48" s="115" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="36" t="s">
         <v>211</v>
       </c>
@@ -14316,16 +14408,16 @@
         <v>213</v>
       </c>
       <c r="C49" s="101" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="D49" s="101" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="E49" s="127" t="s">
-        <v>1480</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="19" t="s">
         <v>215</v>
       </c>
@@ -14333,16 +14425,16 @@
         <v>217</v>
       </c>
       <c r="C50" s="98" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="D50" s="98" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="E50" s="110" t="s">
-        <v>1481</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="20" t="s">
         <v>220</v>
       </c>
@@ -14350,16 +14442,16 @@
         <v>222</v>
       </c>
       <c r="C51" s="99" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D51" s="99" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="E51" s="112" t="s">
-        <v>1482</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="20" t="s">
         <v>224</v>
       </c>
@@ -14367,16 +14459,16 @@
         <v>226</v>
       </c>
       <c r="C52" s="99" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="D52" s="99" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="E52" s="112" t="s">
-        <v>1483</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="20" t="s">
         <v>228</v>
       </c>
@@ -14384,16 +14476,16 @@
         <v>230</v>
       </c>
       <c r="C53" s="99" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="D53" s="99" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="E53" s="112" t="s">
-        <v>1484</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="20" t="s">
         <v>232</v>
       </c>
@@ -14401,16 +14493,16 @@
         <v>234</v>
       </c>
       <c r="C54" s="99" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="D54" s="99" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="E54" s="112" t="s">
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="20" t="s">
         <v>236</v>
       </c>
@@ -14418,16 +14510,16 @@
         <v>238</v>
       </c>
       <c r="C55" s="99" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="D55" s="99" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="E55" s="112" t="s">
-        <v>1486</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="20" t="s">
         <v>240</v>
       </c>
@@ -14435,16 +14527,16 @@
         <v>242</v>
       </c>
       <c r="C56" s="99" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="D56" s="99" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="E56" s="112" t="s">
-        <v>1487</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="21" t="s">
         <v>244</v>
       </c>
@@ -14452,16 +14544,16 @@
         <v>246</v>
       </c>
       <c r="C57" s="100" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="D57" s="100" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="E57" s="114" t="s">
-        <v>1488</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="19" t="s">
         <v>248</v>
       </c>
@@ -14469,16 +14561,16 @@
         <v>250</v>
       </c>
       <c r="C58" s="98" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="D58" s="98" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="E58" s="110" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="20" t="s">
         <v>253</v>
       </c>
@@ -14486,16 +14578,16 @@
         <v>255</v>
       </c>
       <c r="C59" s="99" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="D59" s="99" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="E59" s="112" t="s">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="53" t="s">
         <v>257</v>
       </c>
@@ -14503,16 +14595,16 @@
         <v>259</v>
       </c>
       <c r="C60" s="99" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="D60" s="99" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="E60" s="112" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="20" t="s">
         <v>262</v>
       </c>
@@ -14520,16 +14612,16 @@
         <v>264</v>
       </c>
       <c r="C61" s="99" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="D61" s="99" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="E61" s="112" t="s">
-        <v>1492</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="20" t="s">
         <v>266</v>
       </c>
@@ -14537,16 +14629,16 @@
         <v>268</v>
       </c>
       <c r="C62" s="99" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="D62" s="99" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="E62" s="112" t="s">
-        <v>1493</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="20" t="s">
         <v>270</v>
       </c>
@@ -14554,16 +14646,16 @@
         <v>272</v>
       </c>
       <c r="C63" s="99" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="D63" s="99" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="E63" s="112" t="s">
-        <v>1494</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="20" t="s">
         <v>274</v>
       </c>
@@ -14571,16 +14663,16 @@
         <v>276</v>
       </c>
       <c r="C64" s="99" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="D64" s="99" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="E64" s="112" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="22" t="s">
         <v>278</v>
       </c>
@@ -14588,16 +14680,16 @@
         <v>280</v>
       </c>
       <c r="C65" s="101" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="D65" s="101" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="E65" s="127" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="19" t="s">
         <v>282</v>
       </c>
@@ -14605,16 +14697,16 @@
         <v>284</v>
       </c>
       <c r="C66" s="98" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="D66" s="98" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="E66" s="110" t="s">
-        <v>1497</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" s="115" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" s="115" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="139" t="s">
         <v>287</v>
       </c>
@@ -14622,13 +14714,13 @@
         <v>56</v>
       </c>
       <c r="C67" s="100" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="D67" s="100" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="E67" s="114" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
   </sheetData>
@@ -18153,16 +18245,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="98" t="s">
+        <v>1629</v>
+      </c>
+      <c r="D2" s="110" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E2" s="98" t="s">
         <v>1631</v>
       </c>
-      <c r="D2" s="110" t="s">
+      <c r="F2" s="110" t="s">
         <v>1632</v>
-      </c>
-      <c r="E2" s="98" t="s">
-        <v>1633</v>
-      </c>
-      <c r="F2" s="110" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18173,16 +18265,16 @@
         <v>17</v>
       </c>
       <c r="C3" s="99" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D3" s="112" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E3" s="99" t="s">
         <v>1635</v>
       </c>
-      <c r="D3" s="112" t="s">
+      <c r="F3" s="112" t="s">
         <v>1636</v>
-      </c>
-      <c r="E3" s="99" t="s">
-        <v>1637</v>
-      </c>
-      <c r="F3" s="112" t="s">
-        <v>1638</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18193,16 +18285,16 @@
         <v>23</v>
       </c>
       <c r="C4" s="99" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D4" s="112" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E4" s="99" t="s">
         <v>1639</v>
       </c>
-      <c r="D4" s="112" t="s">
+      <c r="F4" s="112" t="s">
         <v>1640</v>
-      </c>
-      <c r="E4" s="99" t="s">
-        <v>1641</v>
-      </c>
-      <c r="F4" s="112" t="s">
-        <v>1642</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18213,16 +18305,16 @@
         <v>27</v>
       </c>
       <c r="C5" s="99" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D5" s="112" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E5" s="99" t="s">
         <v>1643</v>
       </c>
-      <c r="D5" s="112" t="s">
+      <c r="F5" s="112" t="s">
         <v>1644</v>
-      </c>
-      <c r="E5" s="99" t="s">
-        <v>1645</v>
-      </c>
-      <c r="F5" s="112" t="s">
-        <v>1646</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18233,16 +18325,16 @@
         <v>31</v>
       </c>
       <c r="C6" s="99" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D6" s="112" t="s">
+        <v>1646</v>
+      </c>
+      <c r="E6" s="99" t="s">
         <v>1647</v>
       </c>
-      <c r="D6" s="112" t="s">
+      <c r="F6" s="112" t="s">
         <v>1648</v>
-      </c>
-      <c r="E6" s="99" t="s">
-        <v>1649</v>
-      </c>
-      <c r="F6" s="112" t="s">
-        <v>1650</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18253,16 +18345,16 @@
         <v>36</v>
       </c>
       <c r="C7" s="99" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D7" s="112" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E7" s="99" t="s">
         <v>1651</v>
       </c>
-      <c r="D7" s="112" t="s">
+      <c r="F7" s="112" t="s">
         <v>1652</v>
-      </c>
-      <c r="E7" s="99" t="s">
-        <v>1653</v>
-      </c>
-      <c r="F7" s="112" t="s">
-        <v>1654</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18273,16 +18365,16 @@
         <v>41</v>
       </c>
       <c r="C8" s="99" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D8" s="112" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E8" s="99" t="s">
         <v>1655</v>
       </c>
-      <c r="D8" s="112" t="s">
+      <c r="F8" s="112" t="s">
         <v>1656</v>
-      </c>
-      <c r="E8" s="99" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F8" s="112" t="s">
-        <v>1658</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18293,16 +18385,16 @@
         <v>45</v>
       </c>
       <c r="C9" s="100" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D9" s="114" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E9" s="101" t="s">
         <v>1659</v>
       </c>
-      <c r="D9" s="114" t="s">
+      <c r="F9" s="127" t="s">
         <v>1660</v>
-      </c>
-      <c r="E9" s="101" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F9" s="127" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18313,16 +18405,16 @@
         <v>49</v>
       </c>
       <c r="C10" s="98" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D10" s="110" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E10" s="98" t="s">
         <v>1663</v>
       </c>
-      <c r="D10" s="110" t="s">
+      <c r="F10" s="110" t="s">
         <v>1664</v>
-      </c>
-      <c r="E10" s="98" t="s">
-        <v>1665</v>
-      </c>
-      <c r="F10" s="110" t="s">
-        <v>1666</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18333,16 +18425,16 @@
         <v>54</v>
       </c>
       <c r="C11" s="99" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D11" s="112" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E11" s="99" t="s">
         <v>1667</v>
       </c>
-      <c r="D11" s="112" t="s">
+      <c r="F11" s="112" t="s">
         <v>1668</v>
-      </c>
-      <c r="E11" s="99" t="s">
-        <v>1669</v>
-      </c>
-      <c r="F11" s="112" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18353,16 +18445,16 @@
         <v>59</v>
       </c>
       <c r="C12" s="99" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D12" s="112" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E12" s="99" t="s">
         <v>1671</v>
       </c>
-      <c r="D12" s="112" t="s">
+      <c r="F12" s="112" t="s">
         <v>1672</v>
-      </c>
-      <c r="E12" s="99" t="s">
-        <v>1673</v>
-      </c>
-      <c r="F12" s="112" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18373,16 +18465,16 @@
         <v>63</v>
       </c>
       <c r="C13" s="99" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D13" s="112" t="s">
+        <v>1674</v>
+      </c>
+      <c r="E13" s="99" t="s">
         <v>1675</v>
       </c>
-      <c r="D13" s="112" t="s">
+      <c r="F13" s="112" t="s">
         <v>1676</v>
-      </c>
-      <c r="E13" s="99" t="s">
-        <v>1677</v>
-      </c>
-      <c r="F13" s="112" t="s">
-        <v>1678</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18393,16 +18485,16 @@
         <v>67</v>
       </c>
       <c r="C14" s="99" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D14" s="112" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E14" s="99" t="s">
         <v>1679</v>
       </c>
-      <c r="D14" s="112" t="s">
+      <c r="F14" s="112" t="s">
         <v>1680</v>
-      </c>
-      <c r="E14" s="99" t="s">
-        <v>1681</v>
-      </c>
-      <c r="F14" s="112" t="s">
-        <v>1682</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18413,16 +18505,16 @@
         <v>71</v>
       </c>
       <c r="C15" s="99" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D15" s="112" t="s">
+        <v>1682</v>
+      </c>
+      <c r="E15" s="99" t="s">
         <v>1683</v>
       </c>
-      <c r="D15" s="112" t="s">
+      <c r="F15" s="112" t="s">
         <v>1684</v>
-      </c>
-      <c r="E15" s="99" t="s">
-        <v>1685</v>
-      </c>
-      <c r="F15" s="112" t="s">
-        <v>1686</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18433,16 +18525,16 @@
         <v>75</v>
       </c>
       <c r="C16" s="99" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D16" s="112" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E16" s="99" t="s">
         <v>1687</v>
       </c>
-      <c r="D16" s="112" t="s">
+      <c r="F16" s="112" t="s">
         <v>1688</v>
-      </c>
-      <c r="E16" s="99" t="s">
-        <v>1689</v>
-      </c>
-      <c r="F16" s="112" t="s">
-        <v>1690</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18453,16 +18545,16 @@
         <v>80</v>
       </c>
       <c r="C17" s="100" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D17" s="114" t="s">
+        <v>1690</v>
+      </c>
+      <c r="E17" s="100" t="s">
         <v>1691</v>
       </c>
-      <c r="D17" s="114" t="s">
+      <c r="F17" s="186" t="s">
         <v>1692</v>
-      </c>
-      <c r="E17" s="100" t="s">
-        <v>1693</v>
-      </c>
-      <c r="F17" s="186" t="s">
-        <v>1694</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18473,16 +18565,16 @@
         <v>84</v>
       </c>
       <c r="C18" s="98" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D18" s="110" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E18" s="38" t="s">
         <v>1695</v>
       </c>
-      <c r="D18" s="110" t="s">
+      <c r="F18" s="42" t="s">
         <v>1696</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>1697</v>
-      </c>
-      <c r="F18" s="42" t="s">
-        <v>1698</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18493,16 +18585,16 @@
         <v>89</v>
       </c>
       <c r="C19" s="99" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D19" s="112" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E19" s="99" t="s">
         <v>1699</v>
       </c>
-      <c r="D19" s="112" t="s">
+      <c r="F19" s="112" t="s">
         <v>1700</v>
-      </c>
-      <c r="E19" s="99" t="s">
-        <v>1701</v>
-      </c>
-      <c r="F19" s="112" t="s">
-        <v>1702</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18513,16 +18605,16 @@
         <v>93</v>
       </c>
       <c r="C20" s="99" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D20" s="112" t="s">
+        <v>1702</v>
+      </c>
+      <c r="E20" s="99" t="s">
         <v>1703</v>
       </c>
-      <c r="D20" s="112" t="s">
+      <c r="F20" s="112" t="s">
         <v>1704</v>
-      </c>
-      <c r="E20" s="99" t="s">
-        <v>1705</v>
-      </c>
-      <c r="F20" s="112" t="s">
-        <v>1706</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18533,16 +18625,16 @@
         <v>97</v>
       </c>
       <c r="C21" s="99" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D21" s="112" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E21" s="99" t="s">
         <v>1707</v>
       </c>
-      <c r="D21" s="112" t="s">
+      <c r="F21" s="112" t="s">
         <v>1708</v>
-      </c>
-      <c r="E21" s="99" t="s">
-        <v>1709</v>
-      </c>
-      <c r="F21" s="112" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18553,16 +18645,16 @@
         <v>101</v>
       </c>
       <c r="C22" s="99" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D22" s="112" t="s">
+        <v>1710</v>
+      </c>
+      <c r="E22" s="99" t="s">
         <v>1711</v>
       </c>
-      <c r="D22" s="112" t="s">
+      <c r="F22" s="112" t="s">
         <v>1712</v>
-      </c>
-      <c r="E22" s="99" t="s">
-        <v>1713</v>
-      </c>
-      <c r="F22" s="112" t="s">
-        <v>1714</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18573,16 +18665,16 @@
         <v>105</v>
       </c>
       <c r="C23" s="99" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D23" s="112" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E23" s="99" t="s">
         <v>1715</v>
       </c>
-      <c r="D23" s="112" t="s">
+      <c r="F23" s="112" t="s">
         <v>1716</v>
-      </c>
-      <c r="E23" s="99" t="s">
-        <v>1717</v>
-      </c>
-      <c r="F23" s="112" t="s">
-        <v>1718</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18593,19 +18685,19 @@
         <v>109</v>
       </c>
       <c r="C24" s="99" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D24" s="112" t="s">
+        <v>1718</v>
+      </c>
+      <c r="E24" s="99" t="s">
         <v>1719</v>
       </c>
-      <c r="D24" s="112" t="s">
+      <c r="F24" s="112" t="s">
         <v>1720</v>
       </c>
-      <c r="E24" s="99" t="s">
+      <c r="G24" s="6" t="s">
         <v>1721</v>
-      </c>
-      <c r="F24" s="112" t="s">
-        <v>1722</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>1723</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18616,16 +18708,16 @@
         <v>113</v>
       </c>
       <c r="C25" s="100" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D25" s="114" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E25" s="101" t="s">
         <v>1724</v>
       </c>
-      <c r="D25" s="114" t="s">
+      <c r="F25" s="127" t="s">
         <v>1725</v>
-      </c>
-      <c r="E25" s="101" t="s">
-        <v>1726</v>
-      </c>
-      <c r="F25" s="127" t="s">
-        <v>1727</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18636,16 +18728,16 @@
         <v>117</v>
       </c>
       <c r="C26" s="98" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D26" s="110" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E26" s="98" t="s">
         <v>1728</v>
       </c>
-      <c r="D26" s="110" t="s">
+      <c r="F26" s="110" t="s">
         <v>1729</v>
-      </c>
-      <c r="E26" s="98" t="s">
-        <v>1730</v>
-      </c>
-      <c r="F26" s="110" t="s">
-        <v>1731</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18656,16 +18748,16 @@
         <v>121</v>
       </c>
       <c r="C27" s="99" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D27" s="112" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E27" s="99" t="s">
         <v>1732</v>
       </c>
-      <c r="D27" s="112" t="s">
+      <c r="F27" s="112" t="s">
         <v>1733</v>
-      </c>
-      <c r="E27" s="99" t="s">
-        <v>1734</v>
-      </c>
-      <c r="F27" s="112" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18676,16 +18768,16 @@
         <v>125</v>
       </c>
       <c r="C28" s="99" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D28" s="112" t="s">
+        <v>1735</v>
+      </c>
+      <c r="E28" s="99" t="s">
         <v>1736</v>
       </c>
-      <c r="D28" s="112" t="s">
+      <c r="F28" s="112" t="s">
         <v>1737</v>
-      </c>
-      <c r="E28" s="99" t="s">
-        <v>1738</v>
-      </c>
-      <c r="F28" s="112" t="s">
-        <v>1739</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18696,16 +18788,16 @@
         <v>129</v>
       </c>
       <c r="C29" s="99" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D29" s="112" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E29" s="99" t="s">
         <v>1740</v>
       </c>
-      <c r="D29" s="112" t="s">
+      <c r="F29" s="112" t="s">
         <v>1741</v>
-      </c>
-      <c r="E29" s="99" t="s">
-        <v>1742</v>
-      </c>
-      <c r="F29" s="112" t="s">
-        <v>1743</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18716,16 +18808,16 @@
         <v>133</v>
       </c>
       <c r="C30" s="99" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D30" s="112" t="s">
+        <v>1743</v>
+      </c>
+      <c r="E30" s="99" t="s">
         <v>1744</v>
       </c>
-      <c r="D30" s="112" t="s">
+      <c r="F30" s="112" t="s">
         <v>1745</v>
-      </c>
-      <c r="E30" s="99" t="s">
-        <v>1746</v>
-      </c>
-      <c r="F30" s="112" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18736,16 +18828,16 @@
         <v>137</v>
       </c>
       <c r="C31" s="99" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D31" s="112" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E31" s="99" t="s">
         <v>1748</v>
       </c>
-      <c r="D31" s="112" t="s">
+      <c r="F31" s="112" t="s">
         <v>1749</v>
-      </c>
-      <c r="E31" s="99" t="s">
-        <v>1750</v>
-      </c>
-      <c r="F31" s="112" t="s">
-        <v>1751</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18756,16 +18848,16 @@
         <v>141</v>
       </c>
       <c r="C32" s="99" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D32" s="112" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E32" s="99" t="s">
         <v>1752</v>
       </c>
-      <c r="D32" s="112" t="s">
+      <c r="F32" s="112" t="s">
         <v>1753</v>
-      </c>
-      <c r="E32" s="99" t="s">
-        <v>1754</v>
-      </c>
-      <c r="F32" s="112" t="s">
-        <v>1755</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18776,16 +18868,16 @@
         <v>145</v>
       </c>
       <c r="C33" s="100" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D33" s="114" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E33" s="100" t="s">
         <v>1756</v>
       </c>
-      <c r="D33" s="114" t="s">
+      <c r="F33" s="114" t="s">
         <v>1757</v>
-      </c>
-      <c r="E33" s="100" t="s">
-        <v>1758</v>
-      </c>
-      <c r="F33" s="114" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18796,16 +18888,16 @@
         <v>149</v>
       </c>
       <c r="C34" s="38" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D34" s="42" t="s">
+        <v>1759</v>
+      </c>
+      <c r="E34" s="98" t="s">
         <v>1760</v>
       </c>
-      <c r="D34" s="42" t="s">
+      <c r="F34" s="110" t="s">
         <v>1761</v>
-      </c>
-      <c r="E34" s="98" t="s">
-        <v>1762</v>
-      </c>
-      <c r="F34" s="110" t="s">
-        <v>1763</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18816,16 +18908,16 @@
         <v>154</v>
       </c>
       <c r="C35" s="99" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D35" s="112" t="s">
+        <v>1763</v>
+      </c>
+      <c r="E35" s="99" t="s">
         <v>1764</v>
       </c>
-      <c r="D35" s="112" t="s">
+      <c r="F35" s="112" t="s">
         <v>1765</v>
-      </c>
-      <c r="E35" s="99" t="s">
-        <v>1766</v>
-      </c>
-      <c r="F35" s="112" t="s">
-        <v>1767</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18836,16 +18928,16 @@
         <v>158</v>
       </c>
       <c r="C36" s="185" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D36" s="112" t="s">
+        <v>1767</v>
+      </c>
+      <c r="E36" s="99" t="s">
         <v>1768</v>
       </c>
-      <c r="D36" s="112" t="s">
+      <c r="F36" s="112" t="s">
         <v>1769</v>
-      </c>
-      <c r="E36" s="99" t="s">
-        <v>1770</v>
-      </c>
-      <c r="F36" s="112" t="s">
-        <v>1771</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18856,16 +18948,16 @@
         <v>162</v>
       </c>
       <c r="C37" s="99" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D37" s="112" t="s">
+        <v>1771</v>
+      </c>
+      <c r="E37" s="99" t="s">
         <v>1772</v>
       </c>
-      <c r="D37" s="112" t="s">
+      <c r="F37" s="112" t="s">
         <v>1773</v>
-      </c>
-      <c r="E37" s="99" t="s">
-        <v>1774</v>
-      </c>
-      <c r="F37" s="112" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18876,16 +18968,16 @@
         <v>166</v>
       </c>
       <c r="C38" s="99" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D38" s="112" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E38" s="99" t="s">
         <v>1776</v>
       </c>
-      <c r="D38" s="112" t="s">
+      <c r="F38" s="112" t="s">
         <v>1777</v>
-      </c>
-      <c r="E38" s="99" t="s">
-        <v>1778</v>
-      </c>
-      <c r="F38" s="112" t="s">
-        <v>1779</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18896,16 +18988,16 @@
         <v>170</v>
       </c>
       <c r="C39" s="115" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D39" s="112" t="s">
+        <v>1779</v>
+      </c>
+      <c r="E39" s="99" t="s">
         <v>1780</v>
       </c>
-      <c r="D39" s="112" t="s">
+      <c r="F39" s="112" t="s">
         <v>1781</v>
-      </c>
-      <c r="E39" s="99" t="s">
-        <v>1782</v>
-      </c>
-      <c r="F39" s="112" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18916,16 +19008,16 @@
         <v>174</v>
       </c>
       <c r="C40" s="99" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D40" s="112" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E40" s="99" t="s">
         <v>1784</v>
       </c>
-      <c r="D40" s="112" t="s">
+      <c r="F40" s="112" t="s">
         <v>1785</v>
-      </c>
-      <c r="E40" s="99" t="s">
-        <v>1786</v>
-      </c>
-      <c r="F40" s="112" t="s">
-        <v>1787</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18936,16 +19028,16 @@
         <v>178</v>
       </c>
       <c r="C41" s="101" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D41" s="261" t="s">
+        <v>1787</v>
+      </c>
+      <c r="E41" s="100" t="s">
         <v>1788</v>
       </c>
-      <c r="D41" s="261" t="s">
+      <c r="F41" s="114" t="s">
         <v>1789</v>
-      </c>
-      <c r="E41" s="100" t="s">
-        <v>1790</v>
-      </c>
-      <c r="F41" s="114" t="s">
-        <v>1791</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18956,16 +19048,16 @@
         <v>182</v>
       </c>
       <c r="C42" s="98" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D42" s="110" t="s">
+        <v>1791</v>
+      </c>
+      <c r="E42" s="38" t="s">
         <v>1792</v>
       </c>
-      <c r="D42" s="110" t="s">
+      <c r="F42" s="42" t="s">
         <v>1793</v>
-      </c>
-      <c r="E42" s="38" t="s">
-        <v>1794</v>
-      </c>
-      <c r="F42" s="42" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18976,16 +19068,16 @@
         <v>187</v>
       </c>
       <c r="C43" s="99" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D43" s="112" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E43" s="99" t="s">
         <v>1796</v>
       </c>
-      <c r="D43" s="112" t="s">
+      <c r="F43" s="112" t="s">
         <v>1797</v>
-      </c>
-      <c r="E43" s="99" t="s">
-        <v>1798</v>
-      </c>
-      <c r="F43" s="112" t="s">
-        <v>1799</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18996,16 +19088,16 @@
         <v>191</v>
       </c>
       <c r="C44" s="99" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D44" s="112" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E44" s="99" t="s">
         <v>1800</v>
       </c>
-      <c r="D44" s="112" t="s">
+      <c r="F44" s="112" t="s">
         <v>1801</v>
-      </c>
-      <c r="E44" s="99" t="s">
-        <v>1802</v>
-      </c>
-      <c r="F44" s="112" t="s">
-        <v>1803</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19016,16 +19108,16 @@
         <v>195</v>
       </c>
       <c r="C45" s="99" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D45" s="112" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E45" s="99" t="s">
         <v>1804</v>
       </c>
-      <c r="D45" s="112" t="s">
+      <c r="F45" s="112" t="s">
         <v>1805</v>
-      </c>
-      <c r="E45" s="99" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F45" s="112" t="s">
-        <v>1807</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19036,19 +19128,19 @@
         <v>199</v>
       </c>
       <c r="C46" s="99" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D46" s="112" t="s">
+        <v>1807</v>
+      </c>
+      <c r="E46" s="99" t="s">
         <v>1808</v>
       </c>
-      <c r="D46" s="112" t="s">
+      <c r="F46" s="112" t="s">
         <v>1809</v>
       </c>
-      <c r="E46" s="99" t="s">
+      <c r="G46" s="6" t="s">
         <v>1810</v>
-      </c>
-      <c r="F46" s="112" t="s">
-        <v>1811</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>1812</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19059,16 +19151,16 @@
         <v>203</v>
       </c>
       <c r="C47" s="99" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D47" s="112" t="s">
+        <v>1812</v>
+      </c>
+      <c r="E47" s="99" t="s">
         <v>1813</v>
       </c>
-      <c r="D47" s="112" t="s">
+      <c r="F47" s="112" t="s">
         <v>1814</v>
-      </c>
-      <c r="E47" s="99" t="s">
-        <v>1815</v>
-      </c>
-      <c r="F47" s="112" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19079,19 +19171,19 @@
         <v>207</v>
       </c>
       <c r="C48" s="99" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D48" s="112" t="s">
+        <v>1816</v>
+      </c>
+      <c r="E48" s="99" t="s">
         <v>1817</v>
       </c>
-      <c r="D48" s="112" t="s">
+      <c r="F48" s="112" t="s">
         <v>1818</v>
       </c>
-      <c r="E48" s="99" t="s">
+      <c r="G48" s="6" t="s">
         <v>1819</v>
-      </c>
-      <c r="F48" s="112" t="s">
-        <v>1820</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>1821</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19102,16 +19194,16 @@
         <v>211</v>
       </c>
       <c r="C49" s="100" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D49" s="114" t="s">
+        <v>1821</v>
+      </c>
+      <c r="E49" s="101" t="s">
         <v>1822</v>
       </c>
-      <c r="D49" s="114" t="s">
+      <c r="F49" s="127" t="s">
         <v>1823</v>
-      </c>
-      <c r="E49" s="101" t="s">
-        <v>1824</v>
-      </c>
-      <c r="F49" s="127" t="s">
-        <v>1825</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19122,16 +19214,16 @@
         <v>215</v>
       </c>
       <c r="C50" s="38" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D50" s="42" t="s">
+        <v>1825</v>
+      </c>
+      <c r="E50" s="98" t="s">
         <v>1826</v>
       </c>
-      <c r="D50" s="42" t="s">
+      <c r="F50" s="110" t="s">
         <v>1827</v>
-      </c>
-      <c r="E50" s="98" t="s">
-        <v>1828</v>
-      </c>
-      <c r="F50" s="110" t="s">
-        <v>1829</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19142,16 +19234,16 @@
         <v>220</v>
       </c>
       <c r="C51" s="99" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D51" s="112" t="s">
+        <v>1829</v>
+      </c>
+      <c r="E51" s="99" t="s">
         <v>1830</v>
       </c>
-      <c r="D51" s="112" t="s">
+      <c r="F51" s="112" t="s">
         <v>1831</v>
-      </c>
-      <c r="E51" s="99" t="s">
-        <v>1832</v>
-      </c>
-      <c r="F51" s="112" t="s">
-        <v>1833</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19162,16 +19254,16 @@
         <v>224</v>
       </c>
       <c r="C52" s="99" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D52" s="112" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E52" s="99" t="s">
         <v>1834</v>
       </c>
-      <c r="D52" s="112" t="s">
+      <c r="F52" s="112" t="s">
         <v>1835</v>
-      </c>
-      <c r="E52" s="99" t="s">
-        <v>1836</v>
-      </c>
-      <c r="F52" s="112" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19182,16 +19274,16 @@
         <v>228</v>
       </c>
       <c r="C53" s="99" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D53" s="112" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E53" s="99" t="s">
         <v>1838</v>
       </c>
-      <c r="D53" s="112" t="s">
+      <c r="F53" s="112" t="s">
         <v>1839</v>
-      </c>
-      <c r="E53" s="99" t="s">
-        <v>1840</v>
-      </c>
-      <c r="F53" s="112" t="s">
-        <v>1841</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19202,16 +19294,16 @@
         <v>232</v>
       </c>
       <c r="C54" s="99" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D54" s="112" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E54" s="99" t="s">
         <v>1842</v>
       </c>
-      <c r="D54" s="112" t="s">
+      <c r="F54" s="112" t="s">
         <v>1843</v>
-      </c>
-      <c r="E54" s="99" t="s">
-        <v>1844</v>
-      </c>
-      <c r="F54" s="112" t="s">
-        <v>1845</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19222,16 +19314,16 @@
         <v>236</v>
       </c>
       <c r="C55" s="99" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D55" s="112" t="s">
+        <v>1845</v>
+      </c>
+      <c r="E55" s="99" t="s">
         <v>1846</v>
       </c>
-      <c r="D55" s="112" t="s">
+      <c r="F55" s="112" t="s">
         <v>1847</v>
-      </c>
-      <c r="E55" s="99" t="s">
-        <v>1848</v>
-      </c>
-      <c r="F55" s="112" t="s">
-        <v>1849</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19242,16 +19334,16 @@
         <v>240</v>
       </c>
       <c r="C56" s="99" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D56" s="112" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E56" s="99" t="s">
         <v>1850</v>
       </c>
-      <c r="D56" s="112" t="s">
+      <c r="F56" s="112" t="s">
         <v>1851</v>
-      </c>
-      <c r="E56" s="99" t="s">
-        <v>1852</v>
-      </c>
-      <c r="F56" s="112" t="s">
-        <v>1853</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19262,16 +19354,16 @@
         <v>244</v>
       </c>
       <c r="C57" s="101" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D57" s="127" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E57" s="100" t="s">
         <v>1854</v>
       </c>
-      <c r="D57" s="127" t="s">
+      <c r="F57" s="114" t="s">
         <v>1855</v>
-      </c>
-      <c r="E57" s="100" t="s">
-        <v>1856</v>
-      </c>
-      <c r="F57" s="114" t="s">
-        <v>1857</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19282,16 +19374,16 @@
         <v>248</v>
       </c>
       <c r="C58" s="98" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D58" s="110" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E58" s="38" t="s">
         <v>1858</v>
       </c>
-      <c r="D58" s="110" t="s">
+      <c r="F58" s="42" t="s">
         <v>1859</v>
-      </c>
-      <c r="E58" s="38" t="s">
-        <v>1860</v>
-      </c>
-      <c r="F58" s="42" t="s">
-        <v>1861</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19302,16 +19394,16 @@
         <v>253</v>
       </c>
       <c r="C59" s="99" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D59" s="112" t="s">
+        <v>1861</v>
+      </c>
+      <c r="E59" s="99" t="s">
         <v>1862</v>
       </c>
-      <c r="D59" s="112" t="s">
+      <c r="F59" s="112" t="s">
         <v>1863</v>
-      </c>
-      <c r="E59" s="99" t="s">
-        <v>1864</v>
-      </c>
-      <c r="F59" s="112" t="s">
-        <v>1865</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19322,16 +19414,16 @@
         <v>257</v>
       </c>
       <c r="C60" s="99" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D60" s="112" t="s">
+        <v>1865</v>
+      </c>
+      <c r="E60" s="99" t="s">
         <v>1866</v>
       </c>
-      <c r="D60" s="112" t="s">
+      <c r="F60" s="112" t="s">
         <v>1867</v>
-      </c>
-      <c r="E60" s="99" t="s">
-        <v>1868</v>
-      </c>
-      <c r="F60" s="112" t="s">
-        <v>1869</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19342,16 +19434,16 @@
         <v>262</v>
       </c>
       <c r="C61" s="99" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D61" s="112" t="s">
+        <v>1869</v>
+      </c>
+      <c r="E61" s="99" t="s">
         <v>1870</v>
       </c>
-      <c r="D61" s="112" t="s">
+      <c r="F61" s="112" t="s">
         <v>1871</v>
-      </c>
-      <c r="E61" s="99" t="s">
-        <v>1872</v>
-      </c>
-      <c r="F61" s="112" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19362,16 +19454,16 @@
         <v>266</v>
       </c>
       <c r="C62" s="99" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D62" s="112" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E62" s="99" t="s">
         <v>1874</v>
       </c>
-      <c r="D62" s="112" t="s">
+      <c r="F62" s="112" t="s">
         <v>1875</v>
-      </c>
-      <c r="E62" s="99" t="s">
-        <v>1876</v>
-      </c>
-      <c r="F62" s="112" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19382,16 +19474,16 @@
         <v>270</v>
       </c>
       <c r="C63" s="99" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D63" s="112" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E63" s="99" t="s">
         <v>1878</v>
       </c>
-      <c r="D63" s="112" t="s">
+      <c r="F63" s="112" t="s">
         <v>1879</v>
-      </c>
-      <c r="E63" s="99" t="s">
-        <v>1880</v>
-      </c>
-      <c r="F63" s="112" t="s">
-        <v>1881</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19402,16 +19494,16 @@
         <v>274</v>
       </c>
       <c r="C64" s="99" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D64" s="112" t="s">
+        <v>1881</v>
+      </c>
+      <c r="E64" s="99" t="s">
         <v>1882</v>
       </c>
-      <c r="D64" s="112" t="s">
+      <c r="F64" s="112" t="s">
         <v>1883</v>
-      </c>
-      <c r="E64" s="99" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F64" s="112" t="s">
-        <v>1885</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19422,16 +19514,16 @@
         <v>278</v>
       </c>
       <c r="C65" s="100" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D65" s="114" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E65" s="101" t="s">
         <v>1886</v>
       </c>
-      <c r="D65" s="114" t="s">
+      <c r="F65" s="127" t="s">
         <v>1887</v>
-      </c>
-      <c r="E65" s="101" t="s">
-        <v>1888</v>
-      </c>
-      <c r="F65" s="127" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19442,16 +19534,16 @@
         <v>282</v>
       </c>
       <c r="C66" s="98" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D66" s="110" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E66" s="98" t="s">
         <v>1890</v>
       </c>
-      <c r="D66" s="110" t="s">
+      <c r="F66" s="110" t="s">
         <v>1891</v>
-      </c>
-      <c r="E66" s="98" t="s">
-        <v>1892</v>
-      </c>
-      <c r="F66" s="110" t="s">
-        <v>1893</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19462,16 +19554,16 @@
         <v>287</v>
       </c>
       <c r="C67" s="100" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D67" s="114" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E67" s="100" t="s">
+        <v>1893</v>
+      </c>
+      <c r="F67" s="114" t="s">
         <v>1894</v>
-      </c>
-      <c r="D67" s="114" t="s">
-        <v>1891</v>
-      </c>
-      <c r="E67" s="100" t="s">
-        <v>1895</v>
-      </c>
-      <c r="F67" s="114" t="s">
-        <v>1896</v>
       </c>
     </row>
   </sheetData>
@@ -19524,16 +19616,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="207" t="s">
+        <v>837</v>
+      </c>
+      <c r="D2" s="208" t="s">
+        <v>838</v>
+      </c>
+      <c r="E2" s="209" t="s">
         <v>839</v>
       </c>
-      <c r="D2" s="208" t="s">
+      <c r="F2" s="210" t="s">
         <v>840</v>
-      </c>
-      <c r="E2" s="209" t="s">
-        <v>841</v>
-      </c>
-      <c r="F2" s="210" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19544,16 +19636,16 @@
         <v>17</v>
       </c>
       <c r="C3" s="211" t="s">
+        <v>841</v>
+      </c>
+      <c r="D3" s="212" t="s">
+        <v>842</v>
+      </c>
+      <c r="E3" s="213" t="s">
         <v>843</v>
       </c>
-      <c r="D3" s="212" t="s">
+      <c r="F3" s="214" t="s">
         <v>844</v>
-      </c>
-      <c r="E3" s="213" t="s">
-        <v>845</v>
-      </c>
-      <c r="F3" s="214" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19564,16 +19656,16 @@
         <v>23</v>
       </c>
       <c r="C4" s="211" t="s">
+        <v>845</v>
+      </c>
+      <c r="D4" s="212" t="s">
+        <v>846</v>
+      </c>
+      <c r="E4" s="213" t="s">
         <v>847</v>
       </c>
-      <c r="D4" s="212" t="s">
+      <c r="F4" s="214" t="s">
         <v>848</v>
-      </c>
-      <c r="E4" s="213" t="s">
-        <v>849</v>
-      </c>
-      <c r="F4" s="214" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19584,16 +19676,16 @@
         <v>27</v>
       </c>
       <c r="C5" s="211" t="s">
+        <v>849</v>
+      </c>
+      <c r="D5" s="212" t="s">
+        <v>850</v>
+      </c>
+      <c r="E5" s="213" t="s">
         <v>851</v>
       </c>
-      <c r="D5" s="212" t="s">
+      <c r="F5" s="214" t="s">
         <v>852</v>
-      </c>
-      <c r="E5" s="213" t="s">
-        <v>853</v>
-      </c>
-      <c r="F5" s="214" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19604,16 +19696,16 @@
         <v>31</v>
       </c>
       <c r="C6" s="211" t="s">
+        <v>853</v>
+      </c>
+      <c r="D6" s="212" t="s">
+        <v>854</v>
+      </c>
+      <c r="E6" s="213" t="s">
         <v>855</v>
       </c>
-      <c r="D6" s="212" t="s">
+      <c r="F6" s="214" t="s">
         <v>856</v>
-      </c>
-      <c r="E6" s="213" t="s">
-        <v>857</v>
-      </c>
-      <c r="F6" s="214" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19624,16 +19716,16 @@
         <v>36</v>
       </c>
       <c r="C7" s="211" t="s">
+        <v>857</v>
+      </c>
+      <c r="D7" s="212" t="s">
+        <v>858</v>
+      </c>
+      <c r="E7" s="213" t="s">
         <v>859</v>
       </c>
-      <c r="D7" s="212" t="s">
+      <c r="F7" s="214" t="s">
         <v>860</v>
-      </c>
-      <c r="E7" s="213" t="s">
-        <v>861</v>
-      </c>
-      <c r="F7" s="214" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19644,16 +19736,16 @@
         <v>41</v>
       </c>
       <c r="C8" s="211" t="s">
+        <v>861</v>
+      </c>
+      <c r="D8" s="212" t="s">
+        <v>862</v>
+      </c>
+      <c r="E8" s="213" t="s">
         <v>863</v>
       </c>
-      <c r="D8" s="212" t="s">
+      <c r="F8" s="214" t="s">
         <v>864</v>
-      </c>
-      <c r="E8" s="213" t="s">
-        <v>865</v>
-      </c>
-      <c r="F8" s="214" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19664,16 +19756,16 @@
         <v>45</v>
       </c>
       <c r="C9" s="215" t="s">
+        <v>865</v>
+      </c>
+      <c r="D9" s="216" t="s">
+        <v>866</v>
+      </c>
+      <c r="E9" s="217" t="s">
         <v>867</v>
       </c>
-      <c r="D9" s="216" t="s">
+      <c r="F9" s="218" t="s">
         <v>868</v>
-      </c>
-      <c r="E9" s="217" t="s">
-        <v>869</v>
-      </c>
-      <c r="F9" s="218" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19684,16 +19776,16 @@
         <v>49</v>
       </c>
       <c r="C10" s="219" t="s">
+        <v>869</v>
+      </c>
+      <c r="D10" s="220" t="s">
+        <v>870</v>
+      </c>
+      <c r="E10" s="221" t="s">
         <v>871</v>
       </c>
-      <c r="D10" s="220" t="s">
+      <c r="F10" s="210" t="s">
         <v>872</v>
-      </c>
-      <c r="E10" s="221" t="s">
-        <v>873</v>
-      </c>
-      <c r="F10" s="210" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19704,16 +19796,16 @@
         <v>54</v>
       </c>
       <c r="C11" s="222" t="s">
+        <v>873</v>
+      </c>
+      <c r="D11" s="223" t="s">
+        <v>874</v>
+      </c>
+      <c r="E11" s="224" t="s">
         <v>875</v>
       </c>
-      <c r="D11" s="223" t="s">
+      <c r="F11" s="214" t="s">
         <v>876</v>
-      </c>
-      <c r="E11" s="224" t="s">
-        <v>877</v>
-      </c>
-      <c r="F11" s="214" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19724,16 +19816,16 @@
         <v>59</v>
       </c>
       <c r="C12" s="222" t="s">
+        <v>877</v>
+      </c>
+      <c r="D12" s="223" t="s">
+        <v>878</v>
+      </c>
+      <c r="E12" s="224" t="s">
         <v>879</v>
       </c>
-      <c r="D12" s="223" t="s">
+      <c r="F12" s="214" t="s">
         <v>880</v>
-      </c>
-      <c r="E12" s="224" t="s">
-        <v>881</v>
-      </c>
-      <c r="F12" s="214" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19744,16 +19836,16 @@
         <v>63</v>
       </c>
       <c r="C13" s="222" t="s">
+        <v>881</v>
+      </c>
+      <c r="D13" s="223" t="s">
+        <v>882</v>
+      </c>
+      <c r="E13" s="224" t="s">
         <v>883</v>
       </c>
-      <c r="D13" s="223" t="s">
+      <c r="F13" s="214" t="s">
         <v>884</v>
-      </c>
-      <c r="E13" s="224" t="s">
-        <v>885</v>
-      </c>
-      <c r="F13" s="214" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19764,16 +19856,16 @@
         <v>67</v>
       </c>
       <c r="C14" s="222" t="s">
+        <v>885</v>
+      </c>
+      <c r="D14" s="223" t="s">
+        <v>886</v>
+      </c>
+      <c r="E14" s="224" t="s">
         <v>887</v>
       </c>
-      <c r="D14" s="223" t="s">
+      <c r="F14" s="214" t="s">
         <v>888</v>
-      </c>
-      <c r="E14" s="224" t="s">
-        <v>889</v>
-      </c>
-      <c r="F14" s="214" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19784,16 +19876,16 @@
         <v>71</v>
       </c>
       <c r="C15" s="222" t="s">
+        <v>889</v>
+      </c>
+      <c r="D15" s="223" t="s">
+        <v>890</v>
+      </c>
+      <c r="E15" s="224" t="s">
         <v>891</v>
       </c>
-      <c r="D15" s="223" t="s">
+      <c r="F15" s="214" t="s">
         <v>892</v>
-      </c>
-      <c r="E15" s="224" t="s">
-        <v>893</v>
-      </c>
-      <c r="F15" s="214" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19804,16 +19896,16 @@
         <v>75</v>
       </c>
       <c r="C16" s="222" t="s">
+        <v>893</v>
+      </c>
+      <c r="D16" s="223" t="s">
+        <v>894</v>
+      </c>
+      <c r="E16" s="224" t="s">
         <v>895</v>
       </c>
-      <c r="D16" s="223" t="s">
+      <c r="F16" s="214" t="s">
         <v>896</v>
-      </c>
-      <c r="E16" s="224" t="s">
-        <v>897</v>
-      </c>
-      <c r="F16" s="214" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19824,16 +19916,16 @@
         <v>80</v>
       </c>
       <c r="C17" s="225" t="s">
+        <v>897</v>
+      </c>
+      <c r="D17" s="226" t="s">
+        <v>898</v>
+      </c>
+      <c r="E17" s="227" t="s">
         <v>899</v>
       </c>
-      <c r="D17" s="226" t="s">
+      <c r="F17" s="218" t="s">
         <v>900</v>
-      </c>
-      <c r="E17" s="227" t="s">
-        <v>901</v>
-      </c>
-      <c r="F17" s="218" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19844,16 +19936,16 @@
         <v>84</v>
       </c>
       <c r="C18" s="219" t="s">
+        <v>901</v>
+      </c>
+      <c r="D18" s="220" t="s">
+        <v>902</v>
+      </c>
+      <c r="E18" s="221" t="s">
         <v>903</v>
       </c>
-      <c r="D18" s="220" t="s">
+      <c r="F18" s="210" t="s">
         <v>904</v>
-      </c>
-      <c r="E18" s="221" t="s">
-        <v>905</v>
-      </c>
-      <c r="F18" s="210" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19864,16 +19956,16 @@
         <v>89</v>
       </c>
       <c r="C19" s="222" t="s">
+        <v>905</v>
+      </c>
+      <c r="D19" s="223" t="s">
+        <v>906</v>
+      </c>
+      <c r="E19" s="224" t="s">
         <v>907</v>
       </c>
-      <c r="D19" s="223" t="s">
+      <c r="F19" s="214" t="s">
         <v>908</v>
-      </c>
-      <c r="E19" s="224" t="s">
-        <v>909</v>
-      </c>
-      <c r="F19" s="214" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19884,16 +19976,16 @@
         <v>93</v>
       </c>
       <c r="C20" s="222" t="s">
+        <v>909</v>
+      </c>
+      <c r="D20" s="223" t="s">
+        <v>910</v>
+      </c>
+      <c r="E20" s="224" t="s">
         <v>911</v>
       </c>
-      <c r="D20" s="223" t="s">
+      <c r="F20" s="214" t="s">
         <v>912</v>
-      </c>
-      <c r="E20" s="224" t="s">
-        <v>913</v>
-      </c>
-      <c r="F20" s="214" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19904,16 +19996,16 @@
         <v>97</v>
       </c>
       <c r="C21" s="222" t="s">
+        <v>913</v>
+      </c>
+      <c r="D21" s="223" t="s">
+        <v>914</v>
+      </c>
+      <c r="E21" s="224" t="s">
         <v>915</v>
       </c>
-      <c r="D21" s="223" t="s">
+      <c r="F21" s="214" t="s">
         <v>916</v>
-      </c>
-      <c r="E21" s="224" t="s">
-        <v>917</v>
-      </c>
-      <c r="F21" s="214" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19924,16 +20016,16 @@
         <v>101</v>
       </c>
       <c r="C22" s="222" t="s">
+        <v>917</v>
+      </c>
+      <c r="D22" s="223" t="s">
+        <v>918</v>
+      </c>
+      <c r="E22" s="224" t="s">
         <v>919</v>
       </c>
-      <c r="D22" s="223" t="s">
+      <c r="F22" s="214" t="s">
         <v>920</v>
-      </c>
-      <c r="E22" s="224" t="s">
-        <v>921</v>
-      </c>
-      <c r="F22" s="214" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19944,16 +20036,16 @@
         <v>105</v>
       </c>
       <c r="C23" s="222" t="s">
+        <v>921</v>
+      </c>
+      <c r="D23" s="223" t="s">
+        <v>922</v>
+      </c>
+      <c r="E23" s="224" t="s">
         <v>923</v>
       </c>
-      <c r="D23" s="223" t="s">
+      <c r="F23" s="214" t="s">
         <v>924</v>
-      </c>
-      <c r="E23" s="224" t="s">
-        <v>925</v>
-      </c>
-      <c r="F23" s="214" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19964,16 +20056,16 @@
         <v>109</v>
       </c>
       <c r="C24" s="222" t="s">
+        <v>925</v>
+      </c>
+      <c r="D24" s="223" t="s">
+        <v>926</v>
+      </c>
+      <c r="E24" s="224" t="s">
         <v>927</v>
       </c>
-      <c r="D24" s="223" t="s">
+      <c r="F24" s="214" t="s">
         <v>928</v>
-      </c>
-      <c r="E24" s="224" t="s">
-        <v>929</v>
-      </c>
-      <c r="F24" s="214" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -19984,16 +20076,16 @@
         <v>113</v>
       </c>
       <c r="C25" s="225" t="s">
+        <v>929</v>
+      </c>
+      <c r="D25" s="226" t="s">
+        <v>930</v>
+      </c>
+      <c r="E25" s="227" t="s">
         <v>931</v>
       </c>
-      <c r="D25" s="226" t="s">
+      <c r="F25" s="218" t="s">
         <v>932</v>
-      </c>
-      <c r="E25" s="227" t="s">
-        <v>933</v>
-      </c>
-      <c r="F25" s="218" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20004,16 +20096,16 @@
         <v>117</v>
       </c>
       <c r="C26" s="219" t="s">
+        <v>933</v>
+      </c>
+      <c r="D26" s="220" t="s">
+        <v>934</v>
+      </c>
+      <c r="E26" s="221" t="s">
         <v>935</v>
       </c>
-      <c r="D26" s="220" t="s">
+      <c r="F26" s="210" t="s">
         <v>936</v>
-      </c>
-      <c r="E26" s="221" t="s">
-        <v>937</v>
-      </c>
-      <c r="F26" s="210" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20024,16 +20116,16 @@
         <v>121</v>
       </c>
       <c r="C27" s="222" t="s">
+        <v>937</v>
+      </c>
+      <c r="D27" s="223" t="s">
+        <v>938</v>
+      </c>
+      <c r="E27" s="224" t="s">
         <v>939</v>
       </c>
-      <c r="D27" s="223" t="s">
+      <c r="F27" s="214" t="s">
         <v>940</v>
-      </c>
-      <c r="E27" s="224" t="s">
-        <v>941</v>
-      </c>
-      <c r="F27" s="214" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20044,16 +20136,16 @@
         <v>125</v>
       </c>
       <c r="C28" s="222" t="s">
+        <v>941</v>
+      </c>
+      <c r="D28" s="223" t="s">
+        <v>942</v>
+      </c>
+      <c r="E28" s="224" t="s">
         <v>943</v>
       </c>
-      <c r="D28" s="223" t="s">
+      <c r="F28" s="214" t="s">
         <v>944</v>
-      </c>
-      <c r="E28" s="224" t="s">
-        <v>945</v>
-      </c>
-      <c r="F28" s="214" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20064,16 +20156,16 @@
         <v>129</v>
       </c>
       <c r="C29" s="222" t="s">
+        <v>945</v>
+      </c>
+      <c r="D29" s="223" t="s">
+        <v>946</v>
+      </c>
+      <c r="E29" s="224" t="s">
         <v>947</v>
       </c>
-      <c r="D29" s="223" t="s">
+      <c r="F29" s="214" t="s">
         <v>948</v>
-      </c>
-      <c r="E29" s="224" t="s">
-        <v>949</v>
-      </c>
-      <c r="F29" s="214" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20084,16 +20176,16 @@
         <v>133</v>
       </c>
       <c r="C30" s="222" t="s">
+        <v>949</v>
+      </c>
+      <c r="D30" s="223" t="s">
+        <v>950</v>
+      </c>
+      <c r="E30" s="224" t="s">
         <v>951</v>
       </c>
-      <c r="D30" s="223" t="s">
+      <c r="F30" s="214" t="s">
         <v>952</v>
-      </c>
-      <c r="E30" s="224" t="s">
-        <v>953</v>
-      </c>
-      <c r="F30" s="214" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20104,16 +20196,16 @@
         <v>137</v>
       </c>
       <c r="C31" s="222" t="s">
+        <v>953</v>
+      </c>
+      <c r="D31" s="223" t="s">
+        <v>954</v>
+      </c>
+      <c r="E31" s="224" t="s">
         <v>955</v>
       </c>
-      <c r="D31" s="223" t="s">
+      <c r="F31" s="214" t="s">
         <v>956</v>
-      </c>
-      <c r="E31" s="224" t="s">
-        <v>957</v>
-      </c>
-      <c r="F31" s="214" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20124,16 +20216,16 @@
         <v>141</v>
       </c>
       <c r="C32" s="222" t="s">
+        <v>957</v>
+      </c>
+      <c r="D32" s="223" t="s">
+        <v>958</v>
+      </c>
+      <c r="E32" s="224" t="s">
         <v>959</v>
       </c>
-      <c r="D32" s="223" t="s">
+      <c r="F32" s="214" t="s">
         <v>960</v>
-      </c>
-      <c r="E32" s="224" t="s">
-        <v>961</v>
-      </c>
-      <c r="F32" s="214" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20144,16 +20236,16 @@
         <v>145</v>
       </c>
       <c r="C33" s="225" t="s">
+        <v>961</v>
+      </c>
+      <c r="D33" s="226" t="s">
+        <v>962</v>
+      </c>
+      <c r="E33" s="227" t="s">
         <v>963</v>
       </c>
-      <c r="D33" s="226" t="s">
+      <c r="F33" s="218" t="s">
         <v>964</v>
-      </c>
-      <c r="E33" s="227" t="s">
-        <v>965</v>
-      </c>
-      <c r="F33" s="218" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20164,16 +20256,16 @@
         <v>149</v>
       </c>
       <c r="C34" s="219" t="s">
+        <v>965</v>
+      </c>
+      <c r="D34" s="220" t="s">
+        <v>966</v>
+      </c>
+      <c r="E34" s="221" t="s">
         <v>967</v>
       </c>
-      <c r="D34" s="220" t="s">
+      <c r="F34" s="210" t="s">
         <v>968</v>
-      </c>
-      <c r="E34" s="221" t="s">
-        <v>969</v>
-      </c>
-      <c r="F34" s="210" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20184,16 +20276,16 @@
         <v>154</v>
       </c>
       <c r="C35" s="222" t="s">
+        <v>969</v>
+      </c>
+      <c r="D35" s="223" t="s">
+        <v>970</v>
+      </c>
+      <c r="E35" s="224" t="s">
         <v>971</v>
       </c>
-      <c r="D35" s="223" t="s">
+      <c r="F35" s="228" t="s">
         <v>972</v>
-      </c>
-      <c r="E35" s="224" t="s">
-        <v>973</v>
-      </c>
-      <c r="F35" s="228" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20204,16 +20296,16 @@
         <v>158</v>
       </c>
       <c r="C36" s="222" t="s">
+        <v>973</v>
+      </c>
+      <c r="D36" s="223" t="s">
+        <v>974</v>
+      </c>
+      <c r="E36" s="224" t="s">
         <v>975</v>
       </c>
-      <c r="D36" s="223" t="s">
+      <c r="F36" s="214" t="s">
         <v>976</v>
-      </c>
-      <c r="E36" s="224" t="s">
-        <v>977</v>
-      </c>
-      <c r="F36" s="214" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20224,16 +20316,16 @@
         <v>162</v>
       </c>
       <c r="C37" s="222" t="s">
+        <v>977</v>
+      </c>
+      <c r="D37" s="223" t="s">
+        <v>978</v>
+      </c>
+      <c r="E37" s="164" t="s">
         <v>979</v>
       </c>
-      <c r="D37" s="223" t="s">
+      <c r="F37" s="214" t="s">
         <v>980</v>
-      </c>
-      <c r="E37" s="164" t="s">
-        <v>981</v>
-      </c>
-      <c r="F37" s="214" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="38" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20244,16 +20336,16 @@
         <v>166</v>
       </c>
       <c r="C38" s="222" t="s">
+        <v>981</v>
+      </c>
+      <c r="D38" s="223" t="s">
+        <v>982</v>
+      </c>
+      <c r="E38" s="224" t="s">
         <v>983</v>
       </c>
-      <c r="D38" s="223" t="s">
+      <c r="F38" s="214" t="s">
         <v>984</v>
-      </c>
-      <c r="E38" s="224" t="s">
-        <v>985</v>
-      </c>
-      <c r="F38" s="214" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20264,16 +20356,16 @@
         <v>170</v>
       </c>
       <c r="C39" s="222" t="s">
+        <v>985</v>
+      </c>
+      <c r="D39" s="223" t="s">
+        <v>986</v>
+      </c>
+      <c r="E39" s="224" t="s">
         <v>987</v>
       </c>
-      <c r="D39" s="223" t="s">
+      <c r="F39" s="214" t="s">
         <v>988</v>
-      </c>
-      <c r="E39" s="224" t="s">
-        <v>989</v>
-      </c>
-      <c r="F39" s="214" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="40" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20284,16 +20376,16 @@
         <v>174</v>
       </c>
       <c r="C40" s="222" t="s">
+        <v>989</v>
+      </c>
+      <c r="D40" s="223" t="s">
+        <v>990</v>
+      </c>
+      <c r="E40" s="224" t="s">
         <v>991</v>
       </c>
-      <c r="D40" s="223" t="s">
+      <c r="F40" s="214" t="s">
         <v>992</v>
-      </c>
-      <c r="E40" s="224" t="s">
-        <v>993</v>
-      </c>
-      <c r="F40" s="214" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20304,16 +20396,16 @@
         <v>178</v>
       </c>
       <c r="C41" s="225" t="s">
+        <v>993</v>
+      </c>
+      <c r="D41" s="226" t="s">
+        <v>994</v>
+      </c>
+      <c r="E41" s="227" t="s">
         <v>995</v>
       </c>
-      <c r="D41" s="226" t="s">
+      <c r="F41" s="229" t="s">
         <v>996</v>
-      </c>
-      <c r="E41" s="227" t="s">
-        <v>997</v>
-      </c>
-      <c r="F41" s="229" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20324,16 +20416,16 @@
         <v>182</v>
       </c>
       <c r="C42" s="219" t="s">
+        <v>997</v>
+      </c>
+      <c r="D42" s="220" t="s">
+        <v>998</v>
+      </c>
+      <c r="E42" s="221" t="s">
         <v>999</v>
       </c>
-      <c r="D42" s="220" t="s">
+      <c r="F42" s="210" t="s">
         <v>1000</v>
-      </c>
-      <c r="E42" s="221" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F42" s="210" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20344,16 +20436,16 @@
         <v>187</v>
       </c>
       <c r="C43" s="222" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D43" s="223" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E43" s="224" t="s">
         <v>1003</v>
       </c>
-      <c r="D43" s="223" t="s">
+      <c r="F43" s="214" t="s">
         <v>1004</v>
-      </c>
-      <c r="E43" s="224" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F43" s="214" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="44" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20364,16 +20456,16 @@
         <v>191</v>
       </c>
       <c r="C44" s="222" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D44" s="223" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E44" s="224" t="s">
         <v>1007</v>
       </c>
-      <c r="D44" s="223" t="s">
+      <c r="F44" s="214" t="s">
         <v>1008</v>
-      </c>
-      <c r="E44" s="224" t="s">
-        <v>1009</v>
-      </c>
-      <c r="F44" s="214" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20384,16 +20476,16 @@
         <v>195</v>
       </c>
       <c r="C45" s="222" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D45" s="223" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E45" s="224" t="s">
         <v>1011</v>
       </c>
-      <c r="D45" s="223" t="s">
+      <c r="F45" s="214" t="s">
         <v>1012</v>
-      </c>
-      <c r="E45" s="224" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F45" s="214" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="46" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20404,16 +20496,16 @@
         <v>199</v>
       </c>
       <c r="C46" s="222" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D46" s="223" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E46" s="224" t="s">
         <v>1015</v>
       </c>
-      <c r="D46" s="223" t="s">
+      <c r="F46" s="214" t="s">
         <v>1016</v>
-      </c>
-      <c r="E46" s="224" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F46" s="214" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20424,16 +20516,16 @@
         <v>203</v>
       </c>
       <c r="C47" s="222" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D47" s="223" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E47" s="224" t="s">
         <v>1019</v>
       </c>
-      <c r="D47" s="223" t="s">
+      <c r="F47" s="214" t="s">
         <v>1020</v>
-      </c>
-      <c r="E47" s="224" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F47" s="214" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20444,16 +20536,16 @@
         <v>207</v>
       </c>
       <c r="C48" s="222" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D48" s="223" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E48" s="224" t="s">
         <v>1023</v>
       </c>
-      <c r="D48" s="223" t="s">
+      <c r="F48" s="214" t="s">
         <v>1024</v>
-      </c>
-      <c r="E48" s="224" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F48" s="214" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20464,16 +20556,16 @@
         <v>211</v>
       </c>
       <c r="C49" s="225" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D49" s="226" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E49" s="227" t="s">
         <v>1027</v>
       </c>
-      <c r="D49" s="226" t="s">
+      <c r="F49" s="218" t="s">
         <v>1028</v>
-      </c>
-      <c r="E49" s="227" t="s">
-        <v>1029</v>
-      </c>
-      <c r="F49" s="218" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20484,16 +20576,16 @@
         <v>215</v>
       </c>
       <c r="C50" s="219" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D50" s="220" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E50" s="221" t="s">
         <v>1031</v>
       </c>
-      <c r="D50" s="220" t="s">
+      <c r="F50" s="210" t="s">
         <v>1032</v>
-      </c>
-      <c r="E50" s="221" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F50" s="210" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20504,16 +20596,16 @@
         <v>220</v>
       </c>
       <c r="C51" s="222" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D51" s="223" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E51" s="224" t="s">
         <v>1035</v>
       </c>
-      <c r="D51" s="223" t="s">
+      <c r="F51" s="214" t="s">
         <v>1036</v>
-      </c>
-      <c r="E51" s="224" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F51" s="214" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20524,16 +20616,16 @@
         <v>224</v>
       </c>
       <c r="C52" s="222" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D52" s="223" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E52" s="224" t="s">
         <v>1039</v>
       </c>
-      <c r="D52" s="223" t="s">
+      <c r="F52" s="214" t="s">
         <v>1040</v>
-      </c>
-      <c r="E52" s="224" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F52" s="214" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20544,16 +20636,16 @@
         <v>228</v>
       </c>
       <c r="C53" s="222" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D53" s="223" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E53" s="224" t="s">
         <v>1043</v>
       </c>
-      <c r="D53" s="223" t="s">
+      <c r="F53" s="214" t="s">
         <v>1044</v>
-      </c>
-      <c r="E53" s="224" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F53" s="214" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20564,16 +20656,16 @@
         <v>232</v>
       </c>
       <c r="C54" s="222" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D54" s="223" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E54" s="224" t="s">
         <v>1047</v>
       </c>
-      <c r="D54" s="223" t="s">
+      <c r="F54" s="214" t="s">
         <v>1048</v>
-      </c>
-      <c r="E54" s="224" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F54" s="214" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20584,16 +20676,16 @@
         <v>236</v>
       </c>
       <c r="C55" s="222" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D55" s="223" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E55" s="224" t="s">
         <v>1051</v>
       </c>
-      <c r="D55" s="223" t="s">
+      <c r="F55" s="214" t="s">
         <v>1052</v>
-      </c>
-      <c r="E55" s="224" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F55" s="214" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20604,16 +20696,16 @@
         <v>240</v>
       </c>
       <c r="C56" s="222" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D56" s="223" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E56" s="224" t="s">
         <v>1055</v>
       </c>
-      <c r="D56" s="223" t="s">
+      <c r="F56" s="214" t="s">
         <v>1056</v>
-      </c>
-      <c r="E56" s="224" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F56" s="214" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20624,16 +20716,16 @@
         <v>244</v>
       </c>
       <c r="C57" s="225" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D57" s="226" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E57" s="227" t="s">
         <v>1059</v>
       </c>
-      <c r="D57" s="226" t="s">
+      <c r="F57" s="218" t="s">
         <v>1060</v>
-      </c>
-      <c r="E57" s="227" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F57" s="218" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20644,16 +20736,16 @@
         <v>248</v>
       </c>
       <c r="C58" s="219" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D58" s="220" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E58" s="221" t="s">
         <v>1063</v>
       </c>
-      <c r="D58" s="220" t="s">
+      <c r="F58" s="210" t="s">
         <v>1064</v>
-      </c>
-      <c r="E58" s="221" t="s">
-        <v>1065</v>
-      </c>
-      <c r="F58" s="210" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20664,16 +20756,16 @@
         <v>253</v>
       </c>
       <c r="C59" s="222" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D59" s="223" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E59" s="224" t="s">
         <v>1067</v>
       </c>
-      <c r="D59" s="223" t="s">
+      <c r="F59" s="214" t="s">
         <v>1068</v>
-      </c>
-      <c r="E59" s="224" t="s">
-        <v>1069</v>
-      </c>
-      <c r="F59" s="214" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20684,16 +20776,16 @@
         <v>257</v>
       </c>
       <c r="C60" s="222" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D60" s="223" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E60" s="224" t="s">
         <v>1071</v>
       </c>
-      <c r="D60" s="223" t="s">
+      <c r="F60" s="214" t="s">
         <v>1072</v>
-      </c>
-      <c r="E60" s="224" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F60" s="214" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20704,16 +20796,16 @@
         <v>262</v>
       </c>
       <c r="C61" s="222" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D61" s="223" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E61" s="224" t="s">
         <v>1075</v>
       </c>
-      <c r="D61" s="223" t="s">
+      <c r="F61" s="214" t="s">
         <v>1076</v>
-      </c>
-      <c r="E61" s="224" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F61" s="214" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20724,16 +20816,16 @@
         <v>266</v>
       </c>
       <c r="C62" s="222" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D62" s="223" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E62" s="224" t="s">
         <v>1079</v>
       </c>
-      <c r="D62" s="223" t="s">
+      <c r="F62" s="214" t="s">
         <v>1080</v>
-      </c>
-      <c r="E62" s="224" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F62" s="214" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20744,16 +20836,16 @@
         <v>270</v>
       </c>
       <c r="C63" s="222" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D63" s="223" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E63" s="224" t="s">
         <v>1083</v>
       </c>
-      <c r="D63" s="223" t="s">
+      <c r="F63" s="214" t="s">
         <v>1084</v>
-      </c>
-      <c r="E63" s="224" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F63" s="214" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20764,16 +20856,16 @@
         <v>274</v>
       </c>
       <c r="C64" s="222" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D64" s="223" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E64" s="224" t="s">
         <v>1087</v>
       </c>
-      <c r="D64" s="223" t="s">
+      <c r="F64" s="214" t="s">
         <v>1088</v>
-      </c>
-      <c r="E64" s="224" t="s">
-        <v>1089</v>
-      </c>
-      <c r="F64" s="214" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="66" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20784,16 +20876,16 @@
         <v>278</v>
       </c>
       <c r="C65" s="230" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D65" s="231" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E65" s="232" t="s">
         <v>1091</v>
       </c>
-      <c r="D65" s="231" t="s">
+      <c r="F65" s="233" t="s">
         <v>1092</v>
-      </c>
-      <c r="E65" s="232" t="s">
-        <v>1093</v>
-      </c>
-      <c r="F65" s="233" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="66" spans="1:6" s="115" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -20804,16 +20896,16 @@
         <v>282</v>
       </c>
       <c r="C66" s="219" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D66" s="220" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E66" s="221" t="s">
         <v>1095</v>
       </c>
-      <c r="D66" s="220" t="s">
+      <c r="F66" s="210" t="s">
         <v>1096</v>
-      </c>
-      <c r="E66" s="221" t="s">
-        <v>1097</v>
-      </c>
-      <c r="F66" s="210" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="115" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20824,16 +20916,16 @@
         <v>287</v>
       </c>
       <c r="C67" s="225" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D67" s="226" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E67" s="227" t="s">
         <v>1099</v>
       </c>
-      <c r="D67" s="226" t="s">
+      <c r="F67" s="218" t="s">
         <v>1100</v>
-      </c>
-      <c r="E67" s="227" t="s">
-        <v>1101</v>
-      </c>
-      <c r="F67" s="218" t="s">
-        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -20887,16 +20979,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="234" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D2" s="235" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E2" s="236" t="s">
         <v>1103</v>
       </c>
-      <c r="D2" s="235" t="s">
+      <c r="F2" s="237" t="s">
         <v>1104</v>
-      </c>
-      <c r="E2" s="236" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F2" s="237" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20907,16 +20999,16 @@
         <v>17</v>
       </c>
       <c r="C3" s="238" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D3" s="239" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E3" s="240" t="s">
         <v>1107</v>
       </c>
-      <c r="D3" s="239" t="s">
+      <c r="F3" s="241" t="s">
         <v>1108</v>
-      </c>
-      <c r="E3" s="240" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F3" s="241" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20927,16 +21019,16 @@
         <v>23</v>
       </c>
       <c r="C4" s="238" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D4" s="239" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E4" s="240" t="s">
         <v>1111</v>
       </c>
-      <c r="D4" s="239" t="s">
+      <c r="F4" s="241" t="s">
         <v>1112</v>
-      </c>
-      <c r="E4" s="240" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F4" s="241" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20947,16 +21039,16 @@
         <v>27</v>
       </c>
       <c r="C5" s="238" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D5" s="239" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E5" s="240" t="s">
         <v>1115</v>
       </c>
-      <c r="D5" s="239" t="s">
+      <c r="F5" s="241" t="s">
         <v>1116</v>
-      </c>
-      <c r="E5" s="240" t="s">
-        <v>1117</v>
-      </c>
-      <c r="F5" s="241" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20967,16 +21059,16 @@
         <v>31</v>
       </c>
       <c r="C6" s="238" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D6" s="239" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E6" s="240" t="s">
         <v>1119</v>
       </c>
-      <c r="D6" s="239" t="s">
+      <c r="F6" s="241" t="s">
         <v>1120</v>
-      </c>
-      <c r="E6" s="240" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F6" s="241" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20987,16 +21079,16 @@
         <v>36</v>
       </c>
       <c r="C7" s="238" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D7" s="239" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E7" s="240" t="s">
         <v>1123</v>
       </c>
-      <c r="D7" s="239" t="s">
+      <c r="F7" s="241" t="s">
         <v>1124</v>
-      </c>
-      <c r="E7" s="240" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F7" s="241" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21007,16 +21099,16 @@
         <v>41</v>
       </c>
       <c r="C8" s="238" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D8" s="239" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E8" s="240" t="s">
         <v>1127</v>
       </c>
-      <c r="D8" s="239" t="s">
+      <c r="F8" s="241" t="s">
         <v>1128</v>
-      </c>
-      <c r="E8" s="240" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F8" s="241" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21027,16 +21119,16 @@
         <v>45</v>
       </c>
       <c r="C9" s="242" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D9" s="243" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E9" s="244" t="s">
         <v>1131</v>
       </c>
-      <c r="D9" s="243" t="s">
+      <c r="F9" s="245" t="s">
         <v>1132</v>
-      </c>
-      <c r="E9" s="244" t="s">
-        <v>1133</v>
-      </c>
-      <c r="F9" s="245" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21047,16 +21139,16 @@
         <v>49</v>
       </c>
       <c r="C10" s="246" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D10" s="247" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E10" s="248" t="s">
         <v>1135</v>
       </c>
-      <c r="D10" s="247" t="s">
+      <c r="F10" s="237" t="s">
         <v>1136</v>
-      </c>
-      <c r="E10" s="248" t="s">
-        <v>1137</v>
-      </c>
-      <c r="F10" s="237" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21067,16 +21159,16 @@
         <v>54</v>
       </c>
       <c r="C11" s="249" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D11" s="250" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E11" s="251" t="s">
         <v>1139</v>
       </c>
-      <c r="D11" s="250" t="s">
+      <c r="F11" s="241" t="s">
         <v>1140</v>
-      </c>
-      <c r="E11" s="251" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F11" s="241" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21087,16 +21179,16 @@
         <v>59</v>
       </c>
       <c r="C12" s="249" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D12" s="250" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E12" s="251" t="s">
         <v>1143</v>
       </c>
-      <c r="D12" s="250" t="s">
+      <c r="F12" s="241" t="s">
         <v>1144</v>
-      </c>
-      <c r="E12" s="251" t="s">
-        <v>1145</v>
-      </c>
-      <c r="F12" s="241" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21107,16 +21199,16 @@
         <v>63</v>
       </c>
       <c r="C13" s="249" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D13" s="250" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E13" s="251" t="s">
         <v>1147</v>
       </c>
-      <c r="D13" s="250" t="s">
+      <c r="F13" s="241" t="s">
         <v>1148</v>
-      </c>
-      <c r="E13" s="251" t="s">
-        <v>1149</v>
-      </c>
-      <c r="F13" s="241" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21127,16 +21219,16 @@
         <v>67</v>
       </c>
       <c r="C14" s="249" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D14" s="250" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E14" s="251" t="s">
         <v>1151</v>
       </c>
-      <c r="D14" s="250" t="s">
+      <c r="F14" s="241" t="s">
         <v>1152</v>
-      </c>
-      <c r="E14" s="251" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F14" s="241" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21147,16 +21239,16 @@
         <v>71</v>
       </c>
       <c r="C15" s="249" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D15" s="250" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E15" s="251" t="s">
         <v>1155</v>
       </c>
-      <c r="D15" s="250" t="s">
+      <c r="F15" s="241" t="s">
         <v>1156</v>
-      </c>
-      <c r="E15" s="251" t="s">
-        <v>1157</v>
-      </c>
-      <c r="F15" s="241" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21167,16 +21259,16 @@
         <v>75</v>
       </c>
       <c r="C16" s="249" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D16" s="250" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E16" s="251" t="s">
         <v>1159</v>
       </c>
-      <c r="D16" s="250" t="s">
+      <c r="F16" s="241" t="s">
         <v>1160</v>
-      </c>
-      <c r="E16" s="251" t="s">
-        <v>1161</v>
-      </c>
-      <c r="F16" s="241" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21187,16 +21279,16 @@
         <v>80</v>
       </c>
       <c r="C17" s="252" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D17" s="253" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E17" s="254" t="s">
         <v>1163</v>
       </c>
-      <c r="D17" s="253" t="s">
+      <c r="F17" s="245" t="s">
         <v>1164</v>
-      </c>
-      <c r="E17" s="254" t="s">
-        <v>1165</v>
-      </c>
-      <c r="F17" s="245" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21207,16 +21299,16 @@
         <v>84</v>
       </c>
       <c r="C18" s="246" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D18" s="247" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E18" s="248" t="s">
         <v>1167</v>
       </c>
-      <c r="D18" s="247" t="s">
+      <c r="F18" s="237" t="s">
         <v>1168</v>
-      </c>
-      <c r="E18" s="248" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F18" s="237" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21227,16 +21319,16 @@
         <v>89</v>
       </c>
       <c r="C19" s="249" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D19" s="250" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E19" s="251" t="s">
         <v>1171</v>
       </c>
-      <c r="D19" s="250" t="s">
+      <c r="F19" s="241" t="s">
         <v>1172</v>
-      </c>
-      <c r="E19" s="251" t="s">
-        <v>1173</v>
-      </c>
-      <c r="F19" s="241" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21247,16 +21339,16 @@
         <v>93</v>
       </c>
       <c r="C20" s="249" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D20" s="250" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E20" s="251" t="s">
         <v>1175</v>
       </c>
-      <c r="D20" s="250" t="s">
+      <c r="F20" s="241" t="s">
         <v>1176</v>
-      </c>
-      <c r="E20" s="251" t="s">
-        <v>1177</v>
-      </c>
-      <c r="F20" s="241" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21267,16 +21359,16 @@
         <v>97</v>
       </c>
       <c r="C21" s="249" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D21" s="250" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E21" s="251" t="s">
         <v>1179</v>
       </c>
-      <c r="D21" s="250" t="s">
+      <c r="F21" s="241" t="s">
         <v>1180</v>
-      </c>
-      <c r="E21" s="251" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F21" s="241" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21287,16 +21379,16 @@
         <v>101</v>
       </c>
       <c r="C22" s="249" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D22" s="250" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E22" s="251" t="s">
         <v>1183</v>
       </c>
-      <c r="D22" s="250" t="s">
+      <c r="F22" s="241" t="s">
         <v>1184</v>
-      </c>
-      <c r="E22" s="251" t="s">
-        <v>1185</v>
-      </c>
-      <c r="F22" s="241" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21307,16 +21399,16 @@
         <v>105</v>
       </c>
       <c r="C23" s="249" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D23" s="250" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E23" s="251" t="s">
         <v>1187</v>
       </c>
-      <c r="D23" s="250" t="s">
+      <c r="F23" s="241" t="s">
         <v>1188</v>
-      </c>
-      <c r="E23" s="251" t="s">
-        <v>1189</v>
-      </c>
-      <c r="F23" s="241" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21327,16 +21419,16 @@
         <v>109</v>
       </c>
       <c r="C24" s="249" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D24" s="250" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E24" s="251" t="s">
         <v>1191</v>
       </c>
-      <c r="D24" s="250" t="s">
+      <c r="F24" s="241" t="s">
         <v>1192</v>
-      </c>
-      <c r="E24" s="251" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F24" s="241" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21347,16 +21439,16 @@
         <v>113</v>
       </c>
       <c r="C25" s="252" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D25" s="253" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E25" s="254" t="s">
         <v>1195</v>
       </c>
-      <c r="D25" s="253" t="s">
+      <c r="F25" s="245" t="s">
         <v>1196</v>
-      </c>
-      <c r="E25" s="254" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F25" s="245" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21367,16 +21459,16 @@
         <v>117</v>
       </c>
       <c r="C26" s="246" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D26" s="247" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E26" s="248" t="s">
         <v>1199</v>
       </c>
-      <c r="D26" s="247" t="s">
+      <c r="F26" s="237" t="s">
         <v>1200</v>
-      </c>
-      <c r="E26" s="248" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F26" s="237" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21387,16 +21479,16 @@
         <v>121</v>
       </c>
       <c r="C27" s="249" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D27" s="250" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E27" s="251" t="s">
         <v>1203</v>
       </c>
-      <c r="D27" s="250" t="s">
+      <c r="F27" s="241" t="s">
         <v>1204</v>
-      </c>
-      <c r="E27" s="251" t="s">
-        <v>1205</v>
-      </c>
-      <c r="F27" s="241" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21407,16 +21499,16 @@
         <v>125</v>
       </c>
       <c r="C28" s="249" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D28" s="250" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E28" s="251" t="s">
         <v>1207</v>
       </c>
-      <c r="D28" s="250" t="s">
+      <c r="F28" s="241" t="s">
         <v>1208</v>
-      </c>
-      <c r="E28" s="251" t="s">
-        <v>1209</v>
-      </c>
-      <c r="F28" s="241" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21427,16 +21519,16 @@
         <v>129</v>
       </c>
       <c r="C29" s="249" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D29" s="250" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E29" s="251" t="s">
         <v>1211</v>
       </c>
-      <c r="D29" s="250" t="s">
+      <c r="F29" s="241" t="s">
         <v>1212</v>
-      </c>
-      <c r="E29" s="251" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F29" s="241" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21447,16 +21539,16 @@
         <v>133</v>
       </c>
       <c r="C30" s="249" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D30" s="250" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E30" s="251" t="s">
         <v>1215</v>
       </c>
-      <c r="D30" s="250" t="s">
+      <c r="F30" s="241" t="s">
         <v>1216</v>
-      </c>
-      <c r="E30" s="251" t="s">
-        <v>1217</v>
-      </c>
-      <c r="F30" s="241" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21467,16 +21559,16 @@
         <v>137</v>
       </c>
       <c r="C31" s="249" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D31" s="250" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E31" s="251" t="s">
         <v>1219</v>
       </c>
-      <c r="D31" s="250" t="s">
+      <c r="F31" s="241" t="s">
         <v>1220</v>
-      </c>
-      <c r="E31" s="251" t="s">
-        <v>1221</v>
-      </c>
-      <c r="F31" s="241" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21487,16 +21579,16 @@
         <v>141</v>
       </c>
       <c r="C32" s="249" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D32" s="250" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E32" s="251" t="s">
         <v>1223</v>
       </c>
-      <c r="D32" s="250" t="s">
+      <c r="F32" s="241" t="s">
         <v>1224</v>
-      </c>
-      <c r="E32" s="251" t="s">
-        <v>1225</v>
-      </c>
-      <c r="F32" s="241" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21507,16 +21599,16 @@
         <v>145</v>
       </c>
       <c r="C33" s="252" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D33" s="253" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E33" s="254" t="s">
         <v>1227</v>
       </c>
-      <c r="D33" s="253" t="s">
+      <c r="F33" s="245" t="s">
         <v>1228</v>
-      </c>
-      <c r="E33" s="254" t="s">
-        <v>1229</v>
-      </c>
-      <c r="F33" s="245" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21527,16 +21619,16 @@
         <v>149</v>
       </c>
       <c r="C34" s="246" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D34" s="247" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E34" s="248" t="s">
         <v>1231</v>
       </c>
-      <c r="D34" s="247" t="s">
+      <c r="F34" s="237" t="s">
         <v>1232</v>
-      </c>
-      <c r="E34" s="248" t="s">
-        <v>1233</v>
-      </c>
-      <c r="F34" s="237" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21547,16 +21639,16 @@
         <v>154</v>
       </c>
       <c r="C35" s="249" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D35" s="250" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E35" s="251" t="s">
         <v>1235</v>
       </c>
-      <c r="D35" s="250" t="s">
+      <c r="F35" s="255" t="s">
         <v>1236</v>
-      </c>
-      <c r="E35" s="251" t="s">
-        <v>1237</v>
-      </c>
-      <c r="F35" s="255" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21567,16 +21659,16 @@
         <v>158</v>
       </c>
       <c r="C36" s="249" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D36" s="250" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E36" s="251" t="s">
         <v>1239</v>
       </c>
-      <c r="D36" s="250" t="s">
+      <c r="F36" s="241" t="s">
         <v>1240</v>
-      </c>
-      <c r="E36" s="251" t="s">
-        <v>1241</v>
-      </c>
-      <c r="F36" s="241" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21587,16 +21679,16 @@
         <v>162</v>
       </c>
       <c r="C37" s="249" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D37" s="250" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E37" s="251" t="s">
         <v>1243</v>
       </c>
-      <c r="D37" s="250" t="s">
+      <c r="F37" s="241" t="s">
         <v>1244</v>
-      </c>
-      <c r="E37" s="251" t="s">
-        <v>1245</v>
-      </c>
-      <c r="F37" s="241" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="38" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21607,16 +21699,16 @@
         <v>166</v>
       </c>
       <c r="C38" s="249" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D38" s="250" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E38" s="251" t="s">
         <v>1247</v>
       </c>
-      <c r="D38" s="250" t="s">
+      <c r="F38" s="241" t="s">
         <v>1248</v>
-      </c>
-      <c r="E38" s="251" t="s">
-        <v>1249</v>
-      </c>
-      <c r="F38" s="241" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21627,16 +21719,16 @@
         <v>170</v>
       </c>
       <c r="C39" s="249" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D39" s="250" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E39" s="251" t="s">
         <v>1251</v>
       </c>
-      <c r="D39" s="250" t="s">
+      <c r="F39" s="241" t="s">
         <v>1252</v>
-      </c>
-      <c r="E39" s="251" t="s">
-        <v>1253</v>
-      </c>
-      <c r="F39" s="241" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="40" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21647,16 +21739,16 @@
         <v>174</v>
       </c>
       <c r="C40" s="249" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D40" s="250" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E40" s="251" t="s">
         <v>1255</v>
       </c>
-      <c r="D40" s="250" t="s">
+      <c r="F40" s="241" t="s">
         <v>1256</v>
-      </c>
-      <c r="E40" s="251" t="s">
-        <v>1257</v>
-      </c>
-      <c r="F40" s="241" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21667,16 +21759,16 @@
         <v>178</v>
       </c>
       <c r="C41" s="252" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D41" s="253" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E41" s="254" t="s">
         <v>1259</v>
       </c>
-      <c r="D41" s="253" t="s">
+      <c r="F41" s="256" t="s">
         <v>1260</v>
-      </c>
-      <c r="E41" s="254" t="s">
-        <v>1261</v>
-      </c>
-      <c r="F41" s="256" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21687,16 +21779,16 @@
         <v>182</v>
       </c>
       <c r="C42" s="246" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D42" s="247" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E42" s="248" t="s">
         <v>1263</v>
       </c>
-      <c r="D42" s="247" t="s">
+      <c r="F42" s="237" t="s">
         <v>1264</v>
-      </c>
-      <c r="E42" s="248" t="s">
-        <v>1265</v>
-      </c>
-      <c r="F42" s="237" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21707,16 +21799,16 @@
         <v>187</v>
       </c>
       <c r="C43" s="249" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D43" s="250" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E43" s="251" t="s">
         <v>1267</v>
       </c>
-      <c r="D43" s="250" t="s">
+      <c r="F43" s="241" t="s">
         <v>1268</v>
-      </c>
-      <c r="E43" s="251" t="s">
-        <v>1269</v>
-      </c>
-      <c r="F43" s="241" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="44" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21727,16 +21819,16 @@
         <v>191</v>
       </c>
       <c r="C44" s="249" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D44" s="250" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E44" s="251" t="s">
         <v>1271</v>
       </c>
-      <c r="D44" s="250" t="s">
+      <c r="F44" s="241" t="s">
         <v>1272</v>
-      </c>
-      <c r="E44" s="251" t="s">
-        <v>1273</v>
-      </c>
-      <c r="F44" s="241" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21747,16 +21839,16 @@
         <v>195</v>
       </c>
       <c r="C45" s="249" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D45" s="250" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E45" s="251" t="s">
         <v>1275</v>
       </c>
-      <c r="D45" s="250" t="s">
+      <c r="F45" s="241" t="s">
         <v>1276</v>
-      </c>
-      <c r="E45" s="251" t="s">
-        <v>1277</v>
-      </c>
-      <c r="F45" s="241" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="46" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21767,16 +21859,16 @@
         <v>199</v>
       </c>
       <c r="C46" s="249" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D46" s="250" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E46" s="251" t="s">
         <v>1279</v>
       </c>
-      <c r="D46" s="250" t="s">
+      <c r="F46" s="241" t="s">
         <v>1280</v>
-      </c>
-      <c r="E46" s="251" t="s">
-        <v>1281</v>
-      </c>
-      <c r="F46" s="241" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21787,16 +21879,16 @@
         <v>203</v>
       </c>
       <c r="C47" s="249" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D47" s="250" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E47" s="251" t="s">
         <v>1283</v>
       </c>
-      <c r="D47" s="250" t="s">
+      <c r="F47" s="241" t="s">
         <v>1284</v>
-      </c>
-      <c r="E47" s="251" t="s">
-        <v>1285</v>
-      </c>
-      <c r="F47" s="241" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21807,16 +21899,16 @@
         <v>207</v>
       </c>
       <c r="C48" s="249" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D48" s="250" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E48" s="251" t="s">
         <v>1287</v>
       </c>
-      <c r="D48" s="250" t="s">
+      <c r="F48" s="241" t="s">
         <v>1288</v>
-      </c>
-      <c r="E48" s="251" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F48" s="241" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21827,16 +21919,16 @@
         <v>211</v>
       </c>
       <c r="C49" s="252" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D49" s="253" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E49" s="254" t="s">
         <v>1291</v>
       </c>
-      <c r="D49" s="253" t="s">
+      <c r="F49" s="245" t="s">
         <v>1292</v>
-      </c>
-      <c r="E49" s="254" t="s">
-        <v>1293</v>
-      </c>
-      <c r="F49" s="245" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21847,16 +21939,16 @@
         <v>215</v>
       </c>
       <c r="C50" s="246" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D50" s="247" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E50" s="248" t="s">
         <v>1295</v>
       </c>
-      <c r="D50" s="247" t="s">
+      <c r="F50" s="237" t="s">
         <v>1296</v>
-      </c>
-      <c r="E50" s="248" t="s">
-        <v>1297</v>
-      </c>
-      <c r="F50" s="237" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21867,16 +21959,16 @@
         <v>220</v>
       </c>
       <c r="C51" s="249" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D51" s="250" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E51" s="251" t="s">
         <v>1299</v>
       </c>
-      <c r="D51" s="250" t="s">
+      <c r="F51" s="241" t="s">
         <v>1300</v>
-      </c>
-      <c r="E51" s="251" t="s">
-        <v>1301</v>
-      </c>
-      <c r="F51" s="241" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21887,16 +21979,16 @@
         <v>224</v>
       </c>
       <c r="C52" s="249" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D52" s="250" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E52" s="251" t="s">
         <v>1303</v>
       </c>
-      <c r="D52" s="250" t="s">
+      <c r="F52" s="241" t="s">
         <v>1304</v>
-      </c>
-      <c r="E52" s="251" t="s">
-        <v>1305</v>
-      </c>
-      <c r="F52" s="241" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21907,16 +21999,16 @@
         <v>228</v>
       </c>
       <c r="C53" s="249" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D53" s="250" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E53" s="251" t="s">
         <v>1307</v>
       </c>
-      <c r="D53" s="250" t="s">
+      <c r="F53" s="241" t="s">
         <v>1308</v>
-      </c>
-      <c r="E53" s="251" t="s">
-        <v>1309</v>
-      </c>
-      <c r="F53" s="241" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21927,16 +22019,16 @@
         <v>232</v>
       </c>
       <c r="C54" s="249" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D54" s="250" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E54" s="251" t="s">
         <v>1311</v>
       </c>
-      <c r="D54" s="250" t="s">
+      <c r="F54" s="241" t="s">
         <v>1312</v>
-      </c>
-      <c r="E54" s="251" t="s">
-        <v>1313</v>
-      </c>
-      <c r="F54" s="241" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21947,16 +22039,16 @@
         <v>236</v>
       </c>
       <c r="C55" s="249" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D55" s="250" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E55" s="251" t="s">
         <v>1315</v>
       </c>
-      <c r="D55" s="250" t="s">
+      <c r="F55" s="241" t="s">
         <v>1316</v>
-      </c>
-      <c r="E55" s="251" t="s">
-        <v>1317</v>
-      </c>
-      <c r="F55" s="241" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -21967,16 +22059,16 @@
         <v>240</v>
       </c>
       <c r="C56" s="249" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D56" s="250" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E56" s="251" t="s">
         <v>1319</v>
       </c>
-      <c r="D56" s="250" t="s">
+      <c r="F56" s="241" t="s">
         <v>1320</v>
-      </c>
-      <c r="E56" s="251" t="s">
-        <v>1321</v>
-      </c>
-      <c r="F56" s="241" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21987,16 +22079,16 @@
         <v>244</v>
       </c>
       <c r="C57" s="252" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D57" s="253" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E57" s="254" t="s">
         <v>1323</v>
       </c>
-      <c r="D57" s="253" t="s">
+      <c r="F57" s="245" t="s">
         <v>1324</v>
-      </c>
-      <c r="E57" s="254" t="s">
-        <v>1325</v>
-      </c>
-      <c r="F57" s="245" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="58" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -22007,16 +22099,16 @@
         <v>248</v>
       </c>
       <c r="C58" s="246" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D58" s="247" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E58" s="248" t="s">
         <v>1327</v>
       </c>
-      <c r="D58" s="247" t="s">
+      <c r="F58" s="237" t="s">
         <v>1328</v>
-      </c>
-      <c r="E58" s="248" t="s">
-        <v>1329</v>
-      </c>
-      <c r="F58" s="237" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="59" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -22027,16 +22119,16 @@
         <v>253</v>
       </c>
       <c r="C59" s="249" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D59" s="250" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E59" s="251" t="s">
         <v>1331</v>
       </c>
-      <c r="D59" s="250" t="s">
+      <c r="F59" s="241" t="s">
         <v>1332</v>
-      </c>
-      <c r="E59" s="251" t="s">
-        <v>1333</v>
-      </c>
-      <c r="F59" s="241" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="60" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -22047,16 +22139,16 @@
         <v>257</v>
       </c>
       <c r="C60" s="249" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D60" s="250" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E60" s="251" t="s">
         <v>1335</v>
       </c>
-      <c r="D60" s="250" t="s">
+      <c r="F60" s="241" t="s">
         <v>1336</v>
-      </c>
-      <c r="E60" s="251" t="s">
-        <v>1337</v>
-      </c>
-      <c r="F60" s="241" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -22067,16 +22159,16 @@
         <v>262</v>
       </c>
       <c r="C61" s="249" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D61" s="250" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E61" s="251" t="s">
         <v>1339</v>
       </c>
-      <c r="D61" s="250" t="s">
+      <c r="F61" s="241" t="s">
         <v>1340</v>
-      </c>
-      <c r="E61" s="251" t="s">
-        <v>1341</v>
-      </c>
-      <c r="F61" s="241" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -22087,16 +22179,16 @@
         <v>266</v>
       </c>
       <c r="C62" s="249" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D62" s="250" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E62" s="251" t="s">
         <v>1343</v>
       </c>
-      <c r="D62" s="250" t="s">
+      <c r="F62" s="241" t="s">
         <v>1344</v>
-      </c>
-      <c r="E62" s="251" t="s">
-        <v>1345</v>
-      </c>
-      <c r="F62" s="241" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="63" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -22107,16 +22199,16 @@
         <v>270</v>
       </c>
       <c r="C63" s="249" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D63" s="250" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E63" s="251" t="s">
         <v>1347</v>
       </c>
-      <c r="D63" s="250" t="s">
+      <c r="F63" s="241" t="s">
         <v>1348</v>
-      </c>
-      <c r="E63" s="251" t="s">
-        <v>1349</v>
-      </c>
-      <c r="F63" s="241" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="64" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -22127,16 +22219,16 @@
         <v>274</v>
       </c>
       <c r="C64" s="249" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D64" s="250" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E64" s="251" t="s">
         <v>1351</v>
       </c>
-      <c r="D64" s="250" t="s">
+      <c r="F64" s="241" t="s">
         <v>1352</v>
-      </c>
-      <c r="E64" s="251" t="s">
-        <v>1353</v>
-      </c>
-      <c r="F64" s="241" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="1" customFormat="1" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -22147,16 +22239,16 @@
         <v>278</v>
       </c>
       <c r="C65" s="257" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D65" s="258" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E65" s="259" t="s">
         <v>1355</v>
       </c>
-      <c r="D65" s="258" t="s">
+      <c r="F65" s="260" t="s">
         <v>1356</v>
-      </c>
-      <c r="E65" s="259" t="s">
-        <v>1357</v>
-      </c>
-      <c r="F65" s="260" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -22167,16 +22259,16 @@
         <v>282</v>
       </c>
       <c r="C66" s="246" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D66" s="247" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E66" s="248" t="s">
         <v>1359</v>
       </c>
-      <c r="D66" s="247" t="s">
+      <c r="F66" s="237" t="s">
         <v>1360</v>
-      </c>
-      <c r="E66" s="248" t="s">
-        <v>1361</v>
-      </c>
-      <c r="F66" s="237" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -22187,16 +22279,16 @@
         <v>287</v>
       </c>
       <c r="C67" s="252" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D67" s="253" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E67" s="254" t="s">
         <v>1363</v>
       </c>
-      <c r="D67" s="253" t="s">
+      <c r="F67" s="245" t="s">
         <v>1364</v>
-      </c>
-      <c r="E67" s="254" t="s">
-        <v>1365</v>
-      </c>
-      <c r="F67" s="245" t="s">
-        <v>1366</v>
       </c>
     </row>
   </sheetData>
@@ -22304,7 +22396,7 @@
         <v>724</v>
       </c>
       <c r="F4" s="202" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G4" s="193"/>
     </row>
@@ -22325,7 +22417,7 @@
         <v>728</v>
       </c>
       <c r="F5" s="206" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="G5" s="199"/>
     </row>
